--- a/artfynd/A 9827-2025 artfynd.xlsx
+++ b/artfynd/A 9827-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123675737</v>
+        <v>123675764</v>
       </c>
       <c r="B2" t="n">
-        <v>78775</v>
+        <v>78860</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>540120</v>
+        <v>540428</v>
       </c>
       <c r="R2" t="n">
-        <v>7199910</v>
+        <v>7199871</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>08:23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>08:23</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123675781</v>
+        <v>123675772</v>
       </c>
       <c r="B3" t="n">
-        <v>57851</v>
+        <v>78781</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,47 +799,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>540728</v>
+        <v>540491</v>
       </c>
       <c r="R3" t="n">
-        <v>7200067</v>
+        <v>7199896</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -871,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>07:29</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>07:29</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123675735</v>
+        <v>123675753</v>
       </c>
       <c r="B4" t="n">
-        <v>57481</v>
+        <v>78781</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -924,39 +915,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>540080</v>
+        <v>540320</v>
       </c>
       <c r="R4" t="n">
-        <v>7199959</v>
+        <v>7199929</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -988,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -998,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1025,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123675771</v>
+        <v>123675756</v>
       </c>
       <c r="B5" t="n">
-        <v>57481</v>
+        <v>57640</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1041,27 +1027,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1070,10 +1060,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>540488</v>
+        <v>540336</v>
       </c>
       <c r="R5" t="n">
-        <v>7199896</v>
+        <v>7199942</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1105,7 +1095,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1115,7 +1105,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1142,10 +1132,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123675732</v>
+        <v>123675730</v>
       </c>
       <c r="B6" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1182,10 +1172,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>540171</v>
+        <v>540340</v>
       </c>
       <c r="R6" t="n">
-        <v>7200163</v>
+        <v>7200020</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1217,7 +1207,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1227,7 +1217,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1254,10 +1244,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123675727</v>
+        <v>123675728</v>
       </c>
       <c r="B7" t="n">
-        <v>56691</v>
+        <v>56697</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1299,10 +1289,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>540500</v>
+        <v>540526</v>
       </c>
       <c r="R7" t="n">
-        <v>7199873</v>
+        <v>7199833</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1334,7 +1324,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1344,7 +1334,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1371,10 +1361,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123675722</v>
+        <v>123675739</v>
       </c>
       <c r="B8" t="n">
-        <v>79816</v>
+        <v>78781</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1383,25 +1373,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1411,10 +1401,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>540541</v>
+        <v>540140</v>
       </c>
       <c r="R8" t="n">
-        <v>7199839</v>
+        <v>7199918</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1446,7 +1436,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1456,7 +1446,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1483,10 +1473,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123675718</v>
+        <v>123675752</v>
       </c>
       <c r="B9" t="n">
-        <v>56691</v>
+        <v>57487</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1495,31 +1485,31 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1528,10 +1518,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>540623</v>
+        <v>540320</v>
       </c>
       <c r="R9" t="n">
-        <v>7199942</v>
+        <v>7199929</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1563,7 +1553,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1573,7 +1563,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1603,7 +1593,7 @@
         <v>123675723</v>
       </c>
       <c r="B10" t="n">
-        <v>79885</v>
+        <v>79891</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1712,10 +1702,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123675766</v>
+        <v>123675719</v>
       </c>
       <c r="B11" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1752,10 +1742,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>540428</v>
+        <v>540622</v>
       </c>
       <c r="R11" t="n">
-        <v>7199871</v>
+        <v>7199937</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1787,7 +1777,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>08:23</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1797,7 +1787,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>08:23</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1824,10 +1814,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123675759</v>
+        <v>123675751</v>
       </c>
       <c r="B12" t="n">
-        <v>57851</v>
+        <v>78781</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1836,47 +1826,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>540345</v>
+        <v>540269</v>
       </c>
       <c r="R12" t="n">
-        <v>7199934</v>
+        <v>7199949</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1908,7 +1889,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1918,7 +1899,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1945,10 +1926,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123675754</v>
+        <v>123675725</v>
       </c>
       <c r="B13" t="n">
-        <v>90984</v>
+        <v>78781</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1961,21 +1942,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1985,10 +1966,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>540318</v>
+        <v>540523</v>
       </c>
       <c r="R13" t="n">
-        <v>7199932</v>
+        <v>7199906</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2020,7 +2001,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2030,7 +2011,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2057,10 +2038,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123675768</v>
+        <v>123675750</v>
       </c>
       <c r="B14" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2097,10 +2078,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>540469</v>
+        <v>540220</v>
       </c>
       <c r="R14" t="n">
-        <v>7199898</v>
+        <v>7199934</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2132,7 +2113,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>08:57</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2142,7 +2123,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>08:57</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2169,10 +2150,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123675763</v>
+        <v>123675773</v>
       </c>
       <c r="B15" t="n">
-        <v>77718</v>
+        <v>79891</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2181,25 +2162,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>314</v>
+        <v>6462</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2209,10 +2190,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>540425</v>
+        <v>540495</v>
       </c>
       <c r="R15" t="n">
-        <v>7199890</v>
+        <v>7199932</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2244,7 +2225,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>08:27</t>
+          <t>08:03</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2254,7 +2235,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>08:27</t>
+          <t>08:03</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2281,10 +2262,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123675772</v>
+        <v>123675735</v>
       </c>
       <c r="B16" t="n">
-        <v>78775</v>
+        <v>57487</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2297,34 +2278,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>540491</v>
+        <v>540080</v>
       </c>
       <c r="R16" t="n">
-        <v>7199896</v>
+        <v>7199959</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2356,7 +2342,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2366,7 +2352,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2393,10 +2379,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123675726</v>
+        <v>123675770</v>
       </c>
       <c r="B17" t="n">
-        <v>79885</v>
+        <v>78781</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2405,25 +2391,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2433,10 +2419,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>540524</v>
+        <v>540474</v>
       </c>
       <c r="R17" t="n">
-        <v>7199907</v>
+        <v>7199895</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2468,7 +2454,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2478,7 +2464,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2505,10 +2491,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123675780</v>
+        <v>123675766</v>
       </c>
       <c r="B18" t="n">
-        <v>58159</v>
+        <v>78781</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2517,47 +2503,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103044</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>540723</v>
+        <v>540428</v>
       </c>
       <c r="R18" t="n">
-        <v>7200075</v>
+        <v>7199871</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2589,7 +2566,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>07:29</t>
+          <t>08:23</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2599,7 +2576,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>07:29</t>
+          <t>08:23</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2626,10 +2603,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123675749</v>
+        <v>123675778</v>
       </c>
       <c r="B19" t="n">
-        <v>57497</v>
+        <v>74875</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2642,39 +2619,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>6440</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>540220</v>
+        <v>540666</v>
       </c>
       <c r="R19" t="n">
-        <v>7199936</v>
+        <v>7200065</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2706,7 +2678,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>08:57</t>
+          <t>07:38</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2716,7 +2688,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>08:57</t>
+          <t>07:38</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2743,10 +2715,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123675738</v>
+        <v>123675737</v>
       </c>
       <c r="B20" t="n">
-        <v>78854</v>
+        <v>78781</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2759,21 +2731,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2783,10 +2755,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>540142</v>
+        <v>540120</v>
       </c>
       <c r="R20" t="n">
-        <v>7199918</v>
+        <v>7199910</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2818,7 +2790,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2828,7 +2800,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2855,10 +2827,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123675736</v>
+        <v>123675754</v>
       </c>
       <c r="B21" t="n">
-        <v>78775</v>
+        <v>91001</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2871,21 +2843,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2895,10 +2867,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>540078</v>
+        <v>540318</v>
       </c>
       <c r="R21" t="n">
-        <v>7199948</v>
+        <v>7199932</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2930,7 +2902,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2940,7 +2912,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2967,10 +2939,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123675770</v>
+        <v>123675718</v>
       </c>
       <c r="B22" t="n">
-        <v>78775</v>
+        <v>56697</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2979,38 +2951,43 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>540474</v>
+        <v>540623</v>
       </c>
       <c r="R22" t="n">
-        <v>7199895</v>
+        <v>7199942</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3042,7 +3019,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3052,7 +3029,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3079,10 +3056,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123675739</v>
+        <v>123675757</v>
       </c>
       <c r="B23" t="n">
-        <v>78775</v>
+        <v>57640</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3095,34 +3072,43 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>540140</v>
+        <v>540316</v>
       </c>
       <c r="R23" t="n">
-        <v>7199918</v>
+        <v>7200001</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3154,7 +3140,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3164,7 +3150,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3191,10 +3177,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123675725</v>
+        <v>123675759</v>
       </c>
       <c r="B24" t="n">
-        <v>78775</v>
+        <v>57857</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3203,38 +3189,47 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>540523</v>
+        <v>540345</v>
       </c>
       <c r="R24" t="n">
-        <v>7199906</v>
+        <v>7199934</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3266,7 +3261,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3276,7 +3271,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3303,10 +3298,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123675767</v>
+        <v>123675736</v>
       </c>
       <c r="B25" t="n">
-        <v>78861</v>
+        <v>78781</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3315,25 +3310,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6450</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3343,10 +3338,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>540427</v>
+        <v>540078</v>
       </c>
       <c r="R25" t="n">
-        <v>7199883</v>
+        <v>7199948</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3378,7 +3373,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3388,7 +3383,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3415,10 +3410,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123675778</v>
+        <v>123675738</v>
       </c>
       <c r="B26" t="n">
-        <v>74869</v>
+        <v>78860</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3431,21 +3426,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6440</v>
+        <v>864</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3455,10 +3450,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>540666</v>
+        <v>540142</v>
       </c>
       <c r="R26" t="n">
-        <v>7200065</v>
+        <v>7199918</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3490,7 +3485,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>07:38</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3500,7 +3495,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>07:38</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3527,10 +3522,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123675750</v>
+        <v>123675775</v>
       </c>
       <c r="B27" t="n">
-        <v>78775</v>
+        <v>82568</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3543,21 +3538,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3567,10 +3562,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>540220</v>
+        <v>540545</v>
       </c>
       <c r="R27" t="n">
-        <v>7199934</v>
+        <v>7199990</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3602,7 +3597,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>08:57</t>
+          <t>07:55</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3612,7 +3607,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>08:57</t>
+          <t>07:55</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3639,10 +3634,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123675751</v>
+        <v>123675774</v>
       </c>
       <c r="B28" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3679,10 +3674,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>540269</v>
+        <v>540546</v>
       </c>
       <c r="R28" t="n">
-        <v>7199949</v>
+        <v>7199996</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3714,7 +3709,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>08:54</t>
+          <t>07:56</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3724,7 +3719,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>08:54</t>
+          <t>07:56</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3751,10 +3746,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123675755</v>
+        <v>123675722</v>
       </c>
       <c r="B29" t="n">
-        <v>57634</v>
+        <v>79822</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3763,47 +3758,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103021</v>
+        <v>229497</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>540398</v>
+        <v>540541</v>
       </c>
       <c r="R29" t="n">
-        <v>7199894</v>
+        <v>7199839</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3835,7 +3821,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3845,7 +3831,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3872,10 +3858,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123675730</v>
+        <v>123675732</v>
       </c>
       <c r="B30" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3912,10 +3898,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>540340</v>
+        <v>540171</v>
       </c>
       <c r="R30" t="n">
-        <v>7200020</v>
+        <v>7200163</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3947,7 +3933,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3957,7 +3943,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3984,10 +3970,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123675719</v>
+        <v>123675727</v>
       </c>
       <c r="B31" t="n">
-        <v>78775</v>
+        <v>56697</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3996,38 +3982,43 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>540622</v>
+        <v>540500</v>
       </c>
       <c r="R31" t="n">
-        <v>7199937</v>
+        <v>7199873</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4059,7 +4050,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4069,7 +4060,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4096,10 +4087,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123675753</v>
+        <v>123675763</v>
       </c>
       <c r="B32" t="n">
-        <v>78775</v>
+        <v>77724</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4112,21 +4103,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>314</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4136,10 +4127,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>540320</v>
+        <v>540425</v>
       </c>
       <c r="R32" t="n">
-        <v>7199929</v>
+        <v>7199890</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4171,7 +4162,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>08:27</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4181,7 +4172,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>08:27</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4211,7 +4202,7 @@
         <v>123675769</v>
       </c>
       <c r="B33" t="n">
-        <v>97333</v>
+        <v>97350</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4320,10 +4311,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123675783</v>
+        <v>123675724</v>
       </c>
       <c r="B34" t="n">
-        <v>78775</v>
+        <v>79898</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4332,25 +4323,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4360,10 +4351,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>540760</v>
+        <v>540524</v>
       </c>
       <c r="R34" t="n">
-        <v>7200064</v>
+        <v>7199906</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4395,7 +4386,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4405,7 +4396,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4432,10 +4423,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123675728</v>
+        <v>123675771</v>
       </c>
       <c r="B35" t="n">
-        <v>56691</v>
+        <v>57487</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4444,31 +4435,31 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4477,10 +4468,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>540526</v>
+        <v>540488</v>
       </c>
       <c r="R35" t="n">
-        <v>7199833</v>
+        <v>7199896</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4512,7 +4503,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4522,7 +4513,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4549,10 +4540,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123675773</v>
+        <v>123675779</v>
       </c>
       <c r="B36" t="n">
-        <v>79885</v>
+        <v>57487</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4561,41 +4552,50 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>540495</v>
+        <v>540603</v>
       </c>
       <c r="R36" t="n">
-        <v>7199932</v>
+        <v>7199887</v>
       </c>
       <c r="S36" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4624,7 +4624,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>08:03</t>
+          <t>07:32</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4634,7 +4634,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>08:03</t>
+          <t>07:32</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4661,10 +4661,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123675775</v>
+        <v>123675768</v>
       </c>
       <c r="B37" t="n">
-        <v>82562</v>
+        <v>78781</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4677,21 +4677,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4701,10 +4701,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>540545</v>
+        <v>540469</v>
       </c>
       <c r="R37" t="n">
-        <v>7199990</v>
+        <v>7199898</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4736,7 +4736,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>07:55</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4746,7 +4746,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>07:55</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4773,10 +4773,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123675752</v>
+        <v>123675749</v>
       </c>
       <c r="B38" t="n">
-        <v>57481</v>
+        <v>57503</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4789,16 +4789,16 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -4818,10 +4818,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>540320</v>
+        <v>540220</v>
       </c>
       <c r="R38" t="n">
-        <v>7199929</v>
+        <v>7199936</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4853,7 +4853,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>08:57</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4863,7 +4863,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>08:57</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4890,10 +4890,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123675757</v>
+        <v>123675720</v>
       </c>
       <c r="B39" t="n">
-        <v>57634</v>
+        <v>57487</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4906,31 +4906,27 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -4939,10 +4935,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>540316</v>
+        <v>540612</v>
       </c>
       <c r="R39" t="n">
-        <v>7200001</v>
+        <v>7199895</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4974,7 +4970,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4984,7 +4980,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5011,10 +5007,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123675724</v>
+        <v>123675780</v>
       </c>
       <c r="B40" t="n">
-        <v>79892</v>
+        <v>58165</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5027,34 +5023,43 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6464</v>
+        <v>103044</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>540524</v>
+        <v>540723</v>
       </c>
       <c r="R40" t="n">
-        <v>7199906</v>
+        <v>7200075</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -5086,7 +5091,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>07:29</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5096,7 +5101,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>07:29</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5123,10 +5128,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123675774</v>
+        <v>123675783</v>
       </c>
       <c r="B41" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5163,10 +5168,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>540546</v>
+        <v>540760</v>
       </c>
       <c r="R41" t="n">
-        <v>7199996</v>
+        <v>7200064</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5198,7 +5203,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>07:56</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5208,7 +5213,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>07:56</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5235,10 +5240,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123675762</v>
+        <v>123675761</v>
       </c>
       <c r="B42" t="n">
-        <v>57497</v>
+        <v>78781</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5251,39 +5256,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>540423</v>
+        <v>540369</v>
       </c>
       <c r="R42" t="n">
-        <v>7199851</v>
+        <v>7199910</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5315,7 +5315,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>08:37</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5325,7 +5325,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>08:37</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5352,10 +5352,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123675764</v>
+        <v>123675762</v>
       </c>
       <c r="B43" t="n">
-        <v>78854</v>
+        <v>57503</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5368,34 +5368,39 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>864</v>
+        <v>100049</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>540428</v>
+        <v>540423</v>
       </c>
       <c r="R43" t="n">
-        <v>7199871</v>
+        <v>7199851</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5427,7 +5432,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>08:23</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5437,7 +5442,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>08:23</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5464,10 +5469,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123675761</v>
+        <v>123675767</v>
       </c>
       <c r="B44" t="n">
-        <v>78775</v>
+        <v>78867</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5476,25 +5481,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6450</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5504,10 +5509,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>540369</v>
+        <v>540427</v>
       </c>
       <c r="R44" t="n">
-        <v>7199910</v>
+        <v>7199883</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5539,7 +5544,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>08:37</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5549,7 +5554,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>08:37</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5576,10 +5581,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123675720</v>
+        <v>123675755</v>
       </c>
       <c r="B45" t="n">
-        <v>57481</v>
+        <v>57640</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5592,27 +5597,31 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -5621,10 +5630,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>540612</v>
+        <v>540398</v>
       </c>
       <c r="R45" t="n">
-        <v>7199895</v>
+        <v>7199894</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5656,7 +5665,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5666,7 +5675,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5693,10 +5702,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123675756</v>
+        <v>123675781</v>
       </c>
       <c r="B46" t="n">
-        <v>57634</v>
+        <v>57857</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5705,25 +5714,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -5742,10 +5751,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>540336</v>
+        <v>540728</v>
       </c>
       <c r="R46" t="n">
-        <v>7199942</v>
+        <v>7200067</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5777,7 +5786,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>07:29</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5787,7 +5796,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>07:29</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5814,10 +5823,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123675779</v>
+        <v>123675726</v>
       </c>
       <c r="B47" t="n">
-        <v>57481</v>
+        <v>79891</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5826,50 +5835,41 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>540603</v>
+        <v>540524</v>
       </c>
       <c r="R47" t="n">
-        <v>7199887</v>
+        <v>7199907</v>
       </c>
       <c r="S47" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5898,7 +5898,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>07:32</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5908,7 +5908,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>07:32</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD47" t="b">

--- a/artfynd/A 9827-2025 artfynd.xlsx
+++ b/artfynd/A 9827-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123675764</v>
+        <v>123675756</v>
       </c>
       <c r="B2" t="n">
-        <v>78860</v>
+        <v>57640</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,43 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>864</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>540428</v>
+        <v>540336</v>
       </c>
       <c r="R2" t="n">
-        <v>7199871</v>
+        <v>7199942</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>08:23</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>08:23</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123675772</v>
+        <v>123675764</v>
       </c>
       <c r="B3" t="n">
-        <v>78781</v>
+        <v>78860</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +812,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +836,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>540491</v>
+        <v>540428</v>
       </c>
       <c r="R3" t="n">
-        <v>7199896</v>
+        <v>7199871</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>08:23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +881,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>08:23</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,7 +908,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123675753</v>
+        <v>123675772</v>
       </c>
       <c r="B4" t="n">
         <v>78781</v>
@@ -939,10 +948,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>540320</v>
+        <v>540491</v>
       </c>
       <c r="R4" t="n">
-        <v>7199929</v>
+        <v>7199896</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -974,7 +983,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +993,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123675756</v>
+        <v>123675753</v>
       </c>
       <c r="B5" t="n">
-        <v>57640</v>
+        <v>78781</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,43 +1036,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>540336</v>
+        <v>540320</v>
       </c>
       <c r="R5" t="n">
-        <v>7199942</v>
+        <v>7199929</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -3410,10 +3410,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123675738</v>
+        <v>123675774</v>
       </c>
       <c r="B26" t="n">
-        <v>78860</v>
+        <v>78781</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3426,21 +3426,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3450,10 +3450,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>540142</v>
+        <v>540546</v>
       </c>
       <c r="R26" t="n">
-        <v>7199918</v>
+        <v>7199996</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3485,7 +3485,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>07:56</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3495,7 +3495,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>07:56</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3522,10 +3522,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123675775</v>
+        <v>123675722</v>
       </c>
       <c r="B27" t="n">
-        <v>82568</v>
+        <v>79822</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3534,25 +3534,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1312</v>
+        <v>229497</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3562,10 +3562,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>540545</v>
+        <v>540541</v>
       </c>
       <c r="R27" t="n">
-        <v>7199990</v>
+        <v>7199839</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3597,7 +3597,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>07:55</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3607,7 +3607,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>07:55</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3634,10 +3634,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123675774</v>
+        <v>123675738</v>
       </c>
       <c r="B28" t="n">
-        <v>78781</v>
+        <v>78860</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3650,21 +3650,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3674,10 +3674,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>540546</v>
+        <v>540142</v>
       </c>
       <c r="R28" t="n">
-        <v>7199996</v>
+        <v>7199918</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3709,7 +3709,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>07:56</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3719,7 +3719,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>07:56</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3746,10 +3746,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123675722</v>
+        <v>123675775</v>
       </c>
       <c r="B29" t="n">
-        <v>79822</v>
+        <v>82568</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3758,25 +3758,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>229497</v>
+        <v>1312</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3786,10 +3786,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>540541</v>
+        <v>540545</v>
       </c>
       <c r="R29" t="n">
-        <v>7199839</v>
+        <v>7199990</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3821,7 +3821,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>07:55</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3831,7 +3831,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>07:55</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -5352,10 +5352,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123675762</v>
+        <v>123675767</v>
       </c>
       <c r="B43" t="n">
-        <v>57503</v>
+        <v>78867</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5364,43 +5364,38 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100049</v>
+        <v>6450</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>540423</v>
+        <v>540427</v>
       </c>
       <c r="R43" t="n">
-        <v>7199851</v>
+        <v>7199883</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5432,7 +5427,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5442,7 +5437,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5469,10 +5464,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123675767</v>
+        <v>123675762</v>
       </c>
       <c r="B44" t="n">
-        <v>78867</v>
+        <v>57503</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5481,38 +5476,43 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6450</v>
+        <v>100049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>540427</v>
+        <v>540423</v>
       </c>
       <c r="R44" t="n">
-        <v>7199883</v>
+        <v>7199851</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5544,7 +5544,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5554,7 +5554,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="AD44" t="b">

--- a/artfynd/A 9827-2025 artfynd.xlsx
+++ b/artfynd/A 9827-2025 artfynd.xlsx
@@ -3410,10 +3410,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123675774</v>
+        <v>123675738</v>
       </c>
       <c r="B26" t="n">
-        <v>78781</v>
+        <v>78860</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3426,21 +3426,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3450,10 +3450,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>540546</v>
+        <v>540142</v>
       </c>
       <c r="R26" t="n">
-        <v>7199996</v>
+        <v>7199918</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3485,7 +3485,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>07:56</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3495,7 +3495,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>07:56</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3522,10 +3522,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123675722</v>
+        <v>123675775</v>
       </c>
       <c r="B27" t="n">
-        <v>79822</v>
+        <v>82568</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3534,25 +3534,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>229497</v>
+        <v>1312</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3562,10 +3562,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>540541</v>
+        <v>540545</v>
       </c>
       <c r="R27" t="n">
-        <v>7199839</v>
+        <v>7199990</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3597,7 +3597,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>07:55</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3607,7 +3607,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>07:55</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3634,10 +3634,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123675738</v>
+        <v>123675774</v>
       </c>
       <c r="B28" t="n">
-        <v>78860</v>
+        <v>78781</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3650,21 +3650,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3674,10 +3674,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>540142</v>
+        <v>540546</v>
       </c>
       <c r="R28" t="n">
-        <v>7199918</v>
+        <v>7199996</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3709,7 +3709,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>07:56</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3719,7 +3719,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>07:56</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3746,10 +3746,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123675775</v>
+        <v>123675722</v>
       </c>
       <c r="B29" t="n">
-        <v>82568</v>
+        <v>79822</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3758,25 +3758,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1312</v>
+        <v>229497</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3786,10 +3786,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>540545</v>
+        <v>540541</v>
       </c>
       <c r="R29" t="n">
-        <v>7199990</v>
+        <v>7199839</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3821,7 +3821,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>07:55</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3831,7 +3831,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>07:55</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4773,10 +4773,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123675749</v>
+        <v>123675720</v>
       </c>
       <c r="B38" t="n">
-        <v>57503</v>
+        <v>57487</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4789,16 +4789,16 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -4818,10 +4818,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>540220</v>
+        <v>540612</v>
       </c>
       <c r="R38" t="n">
-        <v>7199936</v>
+        <v>7199895</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4853,7 +4853,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>08:57</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4863,7 +4863,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>08:57</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4890,10 +4890,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123675720</v>
+        <v>123675780</v>
       </c>
       <c r="B39" t="n">
-        <v>57487</v>
+        <v>58165</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4902,20 +4902,20 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>103044</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -4923,10 +4923,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr"/>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -4935,10 +4939,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>540612</v>
+        <v>540723</v>
       </c>
       <c r="R39" t="n">
-        <v>7199895</v>
+        <v>7200075</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4970,7 +4974,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>07:29</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4980,7 +4984,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>07:29</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5007,10 +5011,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123675780</v>
+        <v>123675749</v>
       </c>
       <c r="B40" t="n">
-        <v>58165</v>
+        <v>57503</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5019,20 +5023,20 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>103044</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -5040,14 +5044,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -5056,10 +5056,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>540723</v>
+        <v>540220</v>
       </c>
       <c r="R40" t="n">
-        <v>7200075</v>
+        <v>7199936</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -5091,7 +5091,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>07:29</t>
+          <t>08:57</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>07:29</t>
+          <t>08:57</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5352,10 +5352,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123675767</v>
+        <v>123675762</v>
       </c>
       <c r="B43" t="n">
-        <v>78867</v>
+        <v>57503</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5364,38 +5364,43 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6450</v>
+        <v>100049</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>540427</v>
+        <v>540423</v>
       </c>
       <c r="R43" t="n">
-        <v>7199883</v>
+        <v>7199851</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5427,7 +5432,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5437,7 +5442,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5464,10 +5469,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123675762</v>
+        <v>123675767</v>
       </c>
       <c r="B44" t="n">
-        <v>57503</v>
+        <v>78867</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5476,43 +5481,38 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100049</v>
+        <v>6450</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>540423</v>
+        <v>540427</v>
       </c>
       <c r="R44" t="n">
-        <v>7199851</v>
+        <v>7199883</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5544,7 +5544,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5554,7 +5554,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="AD44" t="b">

--- a/artfynd/A 9827-2025 artfynd.xlsx
+++ b/artfynd/A 9827-2025 artfynd.xlsx
@@ -2150,10 +2150,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123675773</v>
+        <v>123675735</v>
       </c>
       <c r="B15" t="n">
-        <v>79891</v>
+        <v>57487</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2162,38 +2162,43 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>540495</v>
+        <v>540080</v>
       </c>
       <c r="R15" t="n">
-        <v>7199932</v>
+        <v>7199959</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2225,7 +2230,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>08:03</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2235,7 +2240,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>08:03</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2262,10 +2267,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123675735</v>
+        <v>123675773</v>
       </c>
       <c r="B16" t="n">
-        <v>57487</v>
+        <v>79891</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2274,43 +2279,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>540080</v>
+        <v>540495</v>
       </c>
       <c r="R16" t="n">
-        <v>7199959</v>
+        <v>7199932</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2342,7 +2342,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>08:03</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2352,7 +2352,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>08:03</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -4773,10 +4773,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123675720</v>
+        <v>123675749</v>
       </c>
       <c r="B38" t="n">
-        <v>57487</v>
+        <v>57503</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4789,16 +4789,16 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -4818,10 +4818,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>540612</v>
+        <v>540220</v>
       </c>
       <c r="R38" t="n">
-        <v>7199895</v>
+        <v>7199936</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4853,7 +4853,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>08:57</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4863,7 +4863,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>08:57</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4890,10 +4890,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123675780</v>
+        <v>123675720</v>
       </c>
       <c r="B39" t="n">
-        <v>58165</v>
+        <v>57487</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4902,20 +4902,20 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>103044</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -4923,14 +4923,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -4939,10 +4935,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>540723</v>
+        <v>540612</v>
       </c>
       <c r="R39" t="n">
-        <v>7200075</v>
+        <v>7199895</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4974,7 +4970,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>07:29</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4984,7 +4980,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>07:29</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5011,10 +5007,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123675749</v>
+        <v>123675780</v>
       </c>
       <c r="B40" t="n">
-        <v>57503</v>
+        <v>58165</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5023,20 +5019,20 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>103044</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -5044,10 +5040,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr"/>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -5056,10 +5056,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>540220</v>
+        <v>540723</v>
       </c>
       <c r="R40" t="n">
-        <v>7199936</v>
+        <v>7200075</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -5091,7 +5091,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>08:57</t>
+          <t>07:29</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>08:57</t>
+          <t>07:29</t>
         </is>
       </c>
       <c r="AD40" t="b">

--- a/artfynd/A 9827-2025 artfynd.xlsx
+++ b/artfynd/A 9827-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123675756</v>
+        <v>123675737</v>
       </c>
       <c r="B2" t="n">
-        <v>57640</v>
+        <v>78786</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,43 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>540336</v>
+        <v>540120</v>
       </c>
       <c r="R2" t="n">
-        <v>7199942</v>
+        <v>7199910</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -759,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123675764</v>
+        <v>123675738</v>
       </c>
       <c r="B3" t="n">
-        <v>78860</v>
+        <v>78865</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -836,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>540428</v>
+        <v>540142</v>
       </c>
       <c r="R3" t="n">
-        <v>7199871</v>
+        <v>7199918</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -871,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>08:23</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>08:23</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123675772</v>
+        <v>123675773</v>
       </c>
       <c r="B4" t="n">
-        <v>78781</v>
+        <v>79896</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,25 +911,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -948,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>540491</v>
+        <v>540495</v>
       </c>
       <c r="R4" t="n">
-        <v>7199896</v>
+        <v>7199932</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -983,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>08:03</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -993,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>08:03</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1020,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123675753</v>
+        <v>123675759</v>
       </c>
       <c r="B5" t="n">
-        <v>78781</v>
+        <v>57860</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,38 +1023,47 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>540320</v>
+        <v>540345</v>
       </c>
       <c r="R5" t="n">
-        <v>7199929</v>
+        <v>7199934</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1132,10 +1132,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123675730</v>
+        <v>123675779</v>
       </c>
       <c r="B6" t="n">
-        <v>78781</v>
+        <v>57490</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1148,37 +1148,46 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>540340</v>
+        <v>540603</v>
       </c>
       <c r="R6" t="n">
-        <v>7200020</v>
+        <v>7199887</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1207,7 +1216,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>07:32</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1217,7 +1226,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>07:32</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1244,10 +1253,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123675728</v>
+        <v>123675771</v>
       </c>
       <c r="B7" t="n">
-        <v>56697</v>
+        <v>57490</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1256,31 +1265,31 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1289,10 +1298,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>540526</v>
+        <v>540488</v>
       </c>
       <c r="R7" t="n">
-        <v>7199833</v>
+        <v>7199896</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1324,7 +1333,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1334,7 +1343,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1361,10 +1370,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123675739</v>
+        <v>123675757</v>
       </c>
       <c r="B8" t="n">
-        <v>78781</v>
+        <v>57643</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1377,34 +1386,43 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>540140</v>
+        <v>540316</v>
       </c>
       <c r="R8" t="n">
-        <v>7199918</v>
+        <v>7200001</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1436,7 +1454,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1446,7 +1464,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1473,10 +1491,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123675752</v>
+        <v>123675739</v>
       </c>
       <c r="B9" t="n">
-        <v>57487</v>
+        <v>78786</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1489,39 +1507,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>540320</v>
+        <v>540140</v>
       </c>
       <c r="R9" t="n">
-        <v>7199929</v>
+        <v>7199918</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1553,7 +1566,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1563,7 +1576,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1590,10 +1603,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123675723</v>
+        <v>123675719</v>
       </c>
       <c r="B10" t="n">
-        <v>79891</v>
+        <v>78786</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1602,25 +1615,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1630,10 +1643,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>540541</v>
+        <v>540622</v>
       </c>
       <c r="R10" t="n">
-        <v>7199839</v>
+        <v>7199937</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1665,7 +1678,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1675,7 +1688,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1702,10 +1715,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123675719</v>
+        <v>123675756</v>
       </c>
       <c r="B11" t="n">
-        <v>78781</v>
+        <v>57643</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1718,34 +1731,43 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>540622</v>
+        <v>540336</v>
       </c>
       <c r="R11" t="n">
-        <v>7199937</v>
+        <v>7199942</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1777,7 +1799,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1787,7 +1809,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1814,10 +1836,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123675751</v>
+        <v>123675766</v>
       </c>
       <c r="B12" t="n">
-        <v>78781</v>
+        <v>78786</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1854,10 +1876,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>540269</v>
+        <v>540428</v>
       </c>
       <c r="R12" t="n">
-        <v>7199949</v>
+        <v>7199871</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1889,7 +1911,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>08:54</t>
+          <t>08:23</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1899,7 +1921,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>08:54</t>
+          <t>08:23</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1926,10 +1948,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123675725</v>
+        <v>123675720</v>
       </c>
       <c r="B13" t="n">
-        <v>78781</v>
+        <v>57490</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1942,34 +1964,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>540523</v>
+        <v>540612</v>
       </c>
       <c r="R13" t="n">
-        <v>7199906</v>
+        <v>7199895</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2001,7 +2028,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2011,7 +2038,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2038,10 +2065,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123675750</v>
+        <v>123675718</v>
       </c>
       <c r="B14" t="n">
-        <v>78781</v>
+        <v>56700</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2050,38 +2077,43 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>540220</v>
+        <v>540623</v>
       </c>
       <c r="R14" t="n">
-        <v>7199934</v>
+        <v>7199942</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2113,7 +2145,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>08:57</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2123,7 +2155,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>08:57</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2150,10 +2182,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123675735</v>
+        <v>123675726</v>
       </c>
       <c r="B15" t="n">
-        <v>57487</v>
+        <v>79896</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2162,43 +2194,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>540080</v>
+        <v>540524</v>
       </c>
       <c r="R15" t="n">
-        <v>7199959</v>
+        <v>7199907</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2230,7 +2257,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2240,7 +2267,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2267,10 +2294,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123675773</v>
+        <v>123675751</v>
       </c>
       <c r="B16" t="n">
-        <v>79891</v>
+        <v>78786</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2279,25 +2306,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2307,10 +2334,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>540495</v>
+        <v>540269</v>
       </c>
       <c r="R16" t="n">
-        <v>7199932</v>
+        <v>7199949</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2342,7 +2369,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>08:03</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2352,7 +2379,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>08:03</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2379,10 +2406,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123675770</v>
+        <v>123675735</v>
       </c>
       <c r="B17" t="n">
-        <v>78781</v>
+        <v>57490</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2395,34 +2422,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>540474</v>
+        <v>540080</v>
       </c>
       <c r="R17" t="n">
-        <v>7199895</v>
+        <v>7199959</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2454,7 +2486,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2464,7 +2496,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2491,10 +2523,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123675766</v>
+        <v>123675781</v>
       </c>
       <c r="B18" t="n">
-        <v>78781</v>
+        <v>57860</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2503,38 +2535,47 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>540428</v>
+        <v>540728</v>
       </c>
       <c r="R18" t="n">
-        <v>7199871</v>
+        <v>7200067</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2566,7 +2607,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>08:23</t>
+          <t>07:29</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2576,7 +2617,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>08:23</t>
+          <t>07:29</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2603,10 +2644,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123675778</v>
+        <v>123675769</v>
       </c>
       <c r="B19" t="n">
-        <v>74875</v>
+        <v>97367</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2615,25 +2656,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6440</v>
+        <v>221945</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2643,10 +2684,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>540666</v>
+        <v>540475</v>
       </c>
       <c r="R19" t="n">
-        <v>7200065</v>
+        <v>7199900</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2678,7 +2719,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>07:38</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2688,7 +2729,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>07:38</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2715,10 +2756,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123675737</v>
+        <v>123675764</v>
       </c>
       <c r="B20" t="n">
-        <v>78781</v>
+        <v>78865</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2731,21 +2772,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2755,10 +2796,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>540120</v>
+        <v>540428</v>
       </c>
       <c r="R20" t="n">
-        <v>7199910</v>
+        <v>7199871</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2790,7 +2831,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>08:23</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2800,7 +2841,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>08:23</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2827,10 +2868,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123675754</v>
+        <v>123675775</v>
       </c>
       <c r="B21" t="n">
-        <v>91001</v>
+        <v>82573</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2843,21 +2884,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2867,10 +2908,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>540318</v>
+        <v>540545</v>
       </c>
       <c r="R21" t="n">
-        <v>7199932</v>
+        <v>7199990</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2902,7 +2943,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>07:55</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2912,7 +2953,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>07:55</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2939,10 +2980,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123675718</v>
+        <v>123675754</v>
       </c>
       <c r="B22" t="n">
-        <v>56697</v>
+        <v>91006</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2951,43 +2992,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100138</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>540623</v>
+        <v>540318</v>
       </c>
       <c r="R22" t="n">
-        <v>7199942</v>
+        <v>7199932</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3019,7 +3055,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3029,7 +3065,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3056,10 +3092,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123675757</v>
+        <v>123675753</v>
       </c>
       <c r="B23" t="n">
-        <v>57640</v>
+        <v>78786</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3072,43 +3108,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>540316</v>
+        <v>540320</v>
       </c>
       <c r="R23" t="n">
-        <v>7200001</v>
+        <v>7199929</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3140,7 +3167,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3150,7 +3177,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3177,10 +3204,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123675759</v>
+        <v>123675767</v>
       </c>
       <c r="B24" t="n">
-        <v>57857</v>
+        <v>78872</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3193,43 +3220,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103015</v>
+        <v>6450</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Ach.) Parrique</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>540345</v>
+        <v>540427</v>
       </c>
       <c r="R24" t="n">
-        <v>7199934</v>
+        <v>7199883</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3261,7 +3279,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3271,7 +3289,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3298,10 +3316,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123675736</v>
+        <v>123675774</v>
       </c>
       <c r="B25" t="n">
-        <v>78781</v>
+        <v>78786</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3338,10 +3356,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>540078</v>
+        <v>540546</v>
       </c>
       <c r="R25" t="n">
-        <v>7199948</v>
+        <v>7199996</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3373,7 +3391,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>07:56</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3383,7 +3401,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>07:56</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3410,10 +3428,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123675738</v>
+        <v>123675778</v>
       </c>
       <c r="B26" t="n">
-        <v>78860</v>
+        <v>74878</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3426,21 +3444,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>864</v>
+        <v>6440</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3450,10 +3468,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>540142</v>
+        <v>540666</v>
       </c>
       <c r="R26" t="n">
-        <v>7199918</v>
+        <v>7200065</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3485,7 +3503,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>07:38</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3495,7 +3513,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>07:38</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3522,10 +3540,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123675775</v>
+        <v>123675763</v>
       </c>
       <c r="B27" t="n">
-        <v>82568</v>
+        <v>77729</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3538,21 +3556,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1312</v>
+        <v>314</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3562,10 +3580,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>540545</v>
+        <v>540425</v>
       </c>
       <c r="R27" t="n">
-        <v>7199990</v>
+        <v>7199890</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3597,7 +3615,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>07:55</t>
+          <t>08:27</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3607,7 +3625,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>07:55</t>
+          <t>08:27</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3634,10 +3652,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123675774</v>
+        <v>123675780</v>
       </c>
       <c r="B28" t="n">
-        <v>78781</v>
+        <v>58168</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3646,38 +3664,47 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>103044</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>540546</v>
+        <v>540723</v>
       </c>
       <c r="R28" t="n">
-        <v>7199996</v>
+        <v>7200075</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3709,7 +3736,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>07:56</t>
+          <t>07:29</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3719,7 +3746,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>07:56</t>
+          <t>07:29</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3746,10 +3773,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123675722</v>
+        <v>123675761</v>
       </c>
       <c r="B29" t="n">
-        <v>79822</v>
+        <v>78786</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3758,25 +3785,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3786,10 +3813,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>540541</v>
+        <v>540369</v>
       </c>
       <c r="R29" t="n">
-        <v>7199839</v>
+        <v>7199910</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3821,7 +3848,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>08:37</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3831,7 +3858,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>08:37</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3858,10 +3885,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123675732</v>
+        <v>123675736</v>
       </c>
       <c r="B30" t="n">
-        <v>78781</v>
+        <v>78786</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3898,10 +3925,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>540171</v>
+        <v>540078</v>
       </c>
       <c r="R30" t="n">
-        <v>7200163</v>
+        <v>7199948</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3933,7 +3960,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3943,7 +3970,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3970,10 +3997,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123675727</v>
+        <v>123675768</v>
       </c>
       <c r="B31" t="n">
-        <v>56697</v>
+        <v>78786</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3982,43 +4009,38 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>540500</v>
+        <v>540469</v>
       </c>
       <c r="R31" t="n">
-        <v>7199873</v>
+        <v>7199898</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4050,7 +4072,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4060,7 +4082,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4087,10 +4109,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123675763</v>
+        <v>123675749</v>
       </c>
       <c r="B32" t="n">
-        <v>77724</v>
+        <v>57506</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4103,34 +4125,39 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>314</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>540425</v>
+        <v>540220</v>
       </c>
       <c r="R32" t="n">
-        <v>7199890</v>
+        <v>7199936</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4162,7 +4189,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>08:27</t>
+          <t>08:57</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4172,7 +4199,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>08:27</t>
+          <t>08:57</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4199,10 +4226,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123675769</v>
+        <v>123675728</v>
       </c>
       <c r="B33" t="n">
-        <v>97350</v>
+        <v>56700</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4215,34 +4242,39 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>540475</v>
+        <v>540526</v>
       </c>
       <c r="R33" t="n">
-        <v>7199900</v>
+        <v>7199833</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4274,7 +4306,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4284,7 +4316,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4311,10 +4343,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123675724</v>
+        <v>123675722</v>
       </c>
       <c r="B34" t="n">
-        <v>79898</v>
+        <v>79827</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4327,21 +4359,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6464</v>
+        <v>229497</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4351,10 +4383,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>540524</v>
+        <v>540541</v>
       </c>
       <c r="R34" t="n">
-        <v>7199906</v>
+        <v>7199839</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4386,7 +4418,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4396,7 +4428,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4423,10 +4455,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123675771</v>
+        <v>123675723</v>
       </c>
       <c r="B35" t="n">
-        <v>57487</v>
+        <v>79896</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4435,43 +4467,38 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>540488</v>
+        <v>540541</v>
       </c>
       <c r="R35" t="n">
-        <v>7199896</v>
+        <v>7199839</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4503,7 +4530,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4513,7 +4540,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4540,10 +4567,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123675779</v>
+        <v>123675724</v>
       </c>
       <c r="B36" t="n">
-        <v>57487</v>
+        <v>79903</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4552,50 +4579,41 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>540603</v>
+        <v>540524</v>
       </c>
       <c r="R36" t="n">
-        <v>7199887</v>
+        <v>7199906</v>
       </c>
       <c r="S36" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4624,7 +4642,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>07:32</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4634,7 +4652,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>07:32</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4661,10 +4679,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123675768</v>
+        <v>123675770</v>
       </c>
       <c r="B37" t="n">
-        <v>78781</v>
+        <v>78786</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4701,10 +4719,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>540469</v>
+        <v>540474</v>
       </c>
       <c r="R37" t="n">
-        <v>7199898</v>
+        <v>7199895</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4736,7 +4754,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4746,7 +4764,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4773,10 +4791,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123675749</v>
+        <v>123675750</v>
       </c>
       <c r="B38" t="n">
-        <v>57503</v>
+        <v>78786</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4789,29 +4807,24 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
@@ -4821,7 +4834,7 @@
         <v>540220</v>
       </c>
       <c r="R38" t="n">
-        <v>7199936</v>
+        <v>7199934</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4890,10 +4903,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123675720</v>
+        <v>123675725</v>
       </c>
       <c r="B39" t="n">
-        <v>57487</v>
+        <v>78786</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4906,39 +4919,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>540612</v>
+        <v>540523</v>
       </c>
       <c r="R39" t="n">
-        <v>7199895</v>
+        <v>7199906</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4970,7 +4978,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4980,7 +4988,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5007,10 +5015,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123675780</v>
+        <v>123675783</v>
       </c>
       <c r="B40" t="n">
-        <v>58165</v>
+        <v>78786</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5019,47 +5027,38 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>103044</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>540723</v>
+        <v>540760</v>
       </c>
       <c r="R40" t="n">
-        <v>7200075</v>
+        <v>7200064</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -5091,7 +5090,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>07:29</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5101,7 +5100,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>07:29</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5128,10 +5127,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123675783</v>
+        <v>123675727</v>
       </c>
       <c r="B41" t="n">
-        <v>78781</v>
+        <v>56700</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5140,38 +5139,43 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>540760</v>
+        <v>540500</v>
       </c>
       <c r="R41" t="n">
-        <v>7200064</v>
+        <v>7199873</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5203,7 +5207,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5213,7 +5217,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5240,10 +5244,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123675761</v>
+        <v>123675755</v>
       </c>
       <c r="B42" t="n">
-        <v>78781</v>
+        <v>57643</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5256,34 +5260,43 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>540369</v>
+        <v>540398</v>
       </c>
       <c r="R42" t="n">
-        <v>7199910</v>
+        <v>7199894</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5315,7 +5328,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>08:37</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5325,7 +5338,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>08:37</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5352,10 +5365,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123675762</v>
+        <v>123675732</v>
       </c>
       <c r="B43" t="n">
-        <v>57503</v>
+        <v>78786</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5368,39 +5381,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>540423</v>
+        <v>540171</v>
       </c>
       <c r="R43" t="n">
-        <v>7199851</v>
+        <v>7200163</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5432,7 +5440,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5442,7 +5450,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5469,10 +5477,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123675767</v>
+        <v>123675730</v>
       </c>
       <c r="B44" t="n">
-        <v>78867</v>
+        <v>78786</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5481,25 +5489,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6450</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5509,10 +5517,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>540427</v>
+        <v>540340</v>
       </c>
       <c r="R44" t="n">
-        <v>7199883</v>
+        <v>7200020</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5544,7 +5552,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5554,7 +5562,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5581,10 +5589,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123675755</v>
+        <v>123675762</v>
       </c>
       <c r="B45" t="n">
-        <v>57640</v>
+        <v>57506</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5597,31 +5605,27 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="M45" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -5630,10 +5634,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>540398</v>
+        <v>540423</v>
       </c>
       <c r="R45" t="n">
-        <v>7199894</v>
+        <v>7199851</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5665,7 +5669,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5675,7 +5679,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5702,10 +5706,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123675781</v>
+        <v>123675772</v>
       </c>
       <c r="B46" t="n">
-        <v>57857</v>
+        <v>78786</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5714,47 +5718,38 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>540728</v>
+        <v>540491</v>
       </c>
       <c r="R46" t="n">
-        <v>7200067</v>
+        <v>7199896</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5786,7 +5781,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>07:29</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5796,7 +5791,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>07:29</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5823,10 +5818,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123675726</v>
+        <v>123675752</v>
       </c>
       <c r="B47" t="n">
-        <v>79891</v>
+        <v>57490</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5835,38 +5830,43 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>540524</v>
+        <v>540320</v>
       </c>
       <c r="R47" t="n">
-        <v>7199907</v>
+        <v>7199929</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5898,7 +5898,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5908,7 +5908,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AD47" t="b">

--- a/artfynd/A 9827-2025 artfynd.xlsx
+++ b/artfynd/A 9827-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123675737</v>
       </c>
       <c r="B2" t="n">
-        <v>78786</v>
+        <v>78788</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123675738</v>
+        <v>123675762</v>
       </c>
       <c r="B3" t="n">
-        <v>78865</v>
+        <v>57507</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,34 +803,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>864</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>540142</v>
+        <v>540423</v>
       </c>
       <c r="R3" t="n">
-        <v>7199918</v>
+        <v>7199851</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123675773</v>
+        <v>123675752</v>
       </c>
       <c r="B4" t="n">
-        <v>79896</v>
+        <v>57491</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,38 +916,43 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>540495</v>
+        <v>540320</v>
       </c>
       <c r="R4" t="n">
-        <v>7199932</v>
+        <v>7199929</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -974,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>08:03</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +994,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>08:03</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123675759</v>
+        <v>123675761</v>
       </c>
       <c r="B5" t="n">
-        <v>57860</v>
+        <v>78788</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,47 +1033,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>540345</v>
+        <v>540369</v>
       </c>
       <c r="R5" t="n">
-        <v>7199934</v>
+        <v>7199910</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1095,7 +1096,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>08:37</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1105,7 +1106,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>08:37</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1132,10 +1133,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123675779</v>
+        <v>123675767</v>
       </c>
       <c r="B6" t="n">
-        <v>57490</v>
+        <v>78874</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1144,50 +1145,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6450</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>(Ach.) Parrique</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>540603</v>
+        <v>540427</v>
       </c>
       <c r="R6" t="n">
-        <v>7199887</v>
+        <v>7199883</v>
       </c>
       <c r="S6" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1216,7 +1208,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>07:32</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1226,7 +1218,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>07:32</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1253,10 +1245,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123675771</v>
+        <v>123675736</v>
       </c>
       <c r="B7" t="n">
-        <v>57490</v>
+        <v>78788</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1269,39 +1261,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>540488</v>
+        <v>540078</v>
       </c>
       <c r="R7" t="n">
-        <v>7199896</v>
+        <v>7199948</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1333,7 +1320,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1343,7 +1330,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1370,10 +1357,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123675757</v>
+        <v>123675719</v>
       </c>
       <c r="B8" t="n">
-        <v>57643</v>
+        <v>78788</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1386,43 +1373,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>540316</v>
+        <v>540622</v>
       </c>
       <c r="R8" t="n">
-        <v>7200001</v>
+        <v>7199937</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1454,7 +1432,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1464,7 +1442,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1491,10 +1469,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123675739</v>
+        <v>123675769</v>
       </c>
       <c r="B9" t="n">
-        <v>78786</v>
+        <v>97369</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1503,25 +1481,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1531,10 +1509,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>540140</v>
+        <v>540475</v>
       </c>
       <c r="R9" t="n">
-        <v>7199918</v>
+        <v>7199900</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1566,7 +1544,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1576,7 +1554,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1603,10 +1581,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123675719</v>
+        <v>123675723</v>
       </c>
       <c r="B10" t="n">
-        <v>78786</v>
+        <v>79898</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1615,25 +1593,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1643,10 +1621,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>540622</v>
+        <v>540541</v>
       </c>
       <c r="R10" t="n">
-        <v>7199937</v>
+        <v>7199839</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1678,7 +1656,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1688,7 +1666,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1715,10 +1693,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123675756</v>
+        <v>123675738</v>
       </c>
       <c r="B11" t="n">
-        <v>57643</v>
+        <v>78867</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1731,43 +1709,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>864</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Lynge) Ahti</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>540336</v>
+        <v>540142</v>
       </c>
       <c r="R11" t="n">
-        <v>7199942</v>
+        <v>7199918</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1799,7 +1768,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1809,7 +1778,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1836,10 +1805,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123675766</v>
+        <v>123675756</v>
       </c>
       <c r="B12" t="n">
-        <v>78786</v>
+        <v>57644</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1852,34 +1821,43 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>540428</v>
+        <v>540336</v>
       </c>
       <c r="R12" t="n">
-        <v>7199871</v>
+        <v>7199942</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1911,7 +1889,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>08:23</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1921,7 +1899,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>08:23</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1948,10 +1926,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123675720</v>
+        <v>123675764</v>
       </c>
       <c r="B13" t="n">
-        <v>57490</v>
+        <v>78867</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1964,39 +1942,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>864</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>540612</v>
+        <v>540428</v>
       </c>
       <c r="R13" t="n">
-        <v>7199895</v>
+        <v>7199871</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2028,7 +2001,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>08:23</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2038,7 +2011,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>08:23</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2065,10 +2038,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123675718</v>
+        <v>123675751</v>
       </c>
       <c r="B14" t="n">
-        <v>56700</v>
+        <v>78788</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2077,43 +2050,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>540623</v>
+        <v>540269</v>
       </c>
       <c r="R14" t="n">
-        <v>7199942</v>
+        <v>7199949</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2145,7 +2113,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2155,7 +2123,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2182,10 +2150,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123675726</v>
+        <v>123675724</v>
       </c>
       <c r="B15" t="n">
-        <v>79896</v>
+        <v>79905</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2198,21 +2166,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6462</v>
+        <v>6464</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2225,7 +2193,7 @@
         <v>540524</v>
       </c>
       <c r="R15" t="n">
-        <v>7199907</v>
+        <v>7199906</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2294,10 +2262,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123675751</v>
+        <v>123675763</v>
       </c>
       <c r="B16" t="n">
-        <v>78786</v>
+        <v>77731</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2310,21 +2278,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>314</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2334,10 +2302,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>540269</v>
+        <v>540425</v>
       </c>
       <c r="R16" t="n">
-        <v>7199949</v>
+        <v>7199890</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2369,7 +2337,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>08:54</t>
+          <t>08:27</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2379,7 +2347,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>08:54</t>
+          <t>08:27</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2406,10 +2374,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123675735</v>
+        <v>123675778</v>
       </c>
       <c r="B17" t="n">
-        <v>57490</v>
+        <v>74879</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2422,39 +2390,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>540080</v>
+        <v>540666</v>
       </c>
       <c r="R17" t="n">
-        <v>7199959</v>
+        <v>7200065</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2486,7 +2449,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>07:38</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2496,7 +2459,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>07:38</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2523,10 +2486,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123675781</v>
+        <v>123675728</v>
       </c>
       <c r="B18" t="n">
-        <v>57860</v>
+        <v>56700</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2539,31 +2502,27 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103015</v>
+        <v>100138</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2572,10 +2531,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>540728</v>
+        <v>540526</v>
       </c>
       <c r="R18" t="n">
-        <v>7200067</v>
+        <v>7199833</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2607,7 +2566,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>07:29</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2617,7 +2576,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>07:29</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2644,10 +2603,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123675769</v>
+        <v>123675757</v>
       </c>
       <c r="B19" t="n">
-        <v>97367</v>
+        <v>57644</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2656,38 +2615,47 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221945</v>
+        <v>103021</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>540475</v>
+        <v>540316</v>
       </c>
       <c r="R19" t="n">
-        <v>7199900</v>
+        <v>7200001</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2719,7 +2687,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2729,7 +2697,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2756,10 +2724,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123675764</v>
+        <v>123675780</v>
       </c>
       <c r="B20" t="n">
-        <v>78865</v>
+        <v>58169</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2768,38 +2736,47 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>864</v>
+        <v>103044</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>540428</v>
+        <v>540723</v>
       </c>
       <c r="R20" t="n">
-        <v>7199871</v>
+        <v>7200075</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2831,7 +2808,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>08:23</t>
+          <t>07:29</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2841,7 +2818,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>08:23</t>
+          <t>07:29</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2868,10 +2845,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123675775</v>
+        <v>123675759</v>
       </c>
       <c r="B21" t="n">
-        <v>82573</v>
+        <v>57861</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2880,38 +2857,47 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1312</v>
+        <v>103015</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>540545</v>
+        <v>540345</v>
       </c>
       <c r="R21" t="n">
-        <v>7199990</v>
+        <v>7199934</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2943,7 +2929,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>07:55</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2953,7 +2939,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>07:55</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2980,10 +2966,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123675754</v>
+        <v>123675727</v>
       </c>
       <c r="B22" t="n">
-        <v>91006</v>
+        <v>56700</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2992,38 +2978,43 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>100138</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>540318</v>
+        <v>540500</v>
       </c>
       <c r="R22" t="n">
-        <v>7199932</v>
+        <v>7199873</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3055,7 +3046,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3065,7 +3056,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3092,10 +3083,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123675753</v>
+        <v>123675781</v>
       </c>
       <c r="B23" t="n">
-        <v>78786</v>
+        <v>57861</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3104,38 +3095,47 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>540320</v>
+        <v>540728</v>
       </c>
       <c r="R23" t="n">
-        <v>7199929</v>
+        <v>7200067</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3167,7 +3167,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>07:29</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3177,7 +3177,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>07:29</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3204,10 +3204,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123675767</v>
+        <v>123675774</v>
       </c>
       <c r="B24" t="n">
-        <v>78872</v>
+        <v>78788</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3216,25 +3216,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6450</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3244,10 +3244,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>540427</v>
+        <v>540546</v>
       </c>
       <c r="R24" t="n">
-        <v>7199883</v>
+        <v>7199996</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3279,7 +3279,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>07:56</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3289,7 +3289,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>07:56</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3316,10 +3316,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123675774</v>
+        <v>123675753</v>
       </c>
       <c r="B25" t="n">
-        <v>78786</v>
+        <v>78788</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3356,10 +3356,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>540546</v>
+        <v>540320</v>
       </c>
       <c r="R25" t="n">
-        <v>7199996</v>
+        <v>7199929</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3391,7 +3391,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>07:56</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>07:56</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3428,10 +3428,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123675778</v>
+        <v>123675773</v>
       </c>
       <c r="B26" t="n">
-        <v>74878</v>
+        <v>79898</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3440,25 +3440,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6440</v>
+        <v>6462</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3468,10 +3468,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>540666</v>
+        <v>540495</v>
       </c>
       <c r="R26" t="n">
-        <v>7200065</v>
+        <v>7199932</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3503,7 +3503,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>07:38</t>
+          <t>08:03</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3513,7 +3513,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>07:38</t>
+          <t>08:03</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3540,10 +3540,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123675763</v>
+        <v>123675735</v>
       </c>
       <c r="B27" t="n">
-        <v>77729</v>
+        <v>57491</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3556,34 +3556,39 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>314</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>540425</v>
+        <v>540080</v>
       </c>
       <c r="R27" t="n">
-        <v>7199890</v>
+        <v>7199959</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3615,7 +3620,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>08:27</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3625,7 +3630,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>08:27</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3652,10 +3657,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123675780</v>
+        <v>123675771</v>
       </c>
       <c r="B28" t="n">
-        <v>58168</v>
+        <v>57491</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3664,20 +3669,20 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103044</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3685,14 +3690,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3701,10 +3702,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>540723</v>
+        <v>540488</v>
       </c>
       <c r="R28" t="n">
-        <v>7200075</v>
+        <v>7199896</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3736,7 +3737,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>07:29</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3746,7 +3747,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>07:29</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3773,10 +3774,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123675761</v>
+        <v>123675726</v>
       </c>
       <c r="B29" t="n">
-        <v>78786</v>
+        <v>79898</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3785,25 +3786,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3813,10 +3814,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>540369</v>
+        <v>540524</v>
       </c>
       <c r="R29" t="n">
-        <v>7199910</v>
+        <v>7199907</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3848,7 +3849,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>08:37</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3858,7 +3859,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>08:37</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3885,10 +3886,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123675736</v>
+        <v>123675718</v>
       </c>
       <c r="B30" t="n">
-        <v>78786</v>
+        <v>56700</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3897,38 +3898,43 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>540078</v>
+        <v>540623</v>
       </c>
       <c r="R30" t="n">
-        <v>7199948</v>
+        <v>7199942</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3960,7 +3966,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3970,7 +3976,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3997,10 +4003,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123675768</v>
+        <v>123675775</v>
       </c>
       <c r="B31" t="n">
-        <v>78786</v>
+        <v>82575</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4013,21 +4019,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4037,10 +4043,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>540469</v>
+        <v>540545</v>
       </c>
       <c r="R31" t="n">
-        <v>7199898</v>
+        <v>7199990</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4072,7 +4078,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>07:55</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4082,7 +4088,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>07:55</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4109,10 +4115,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123675749</v>
+        <v>123675779</v>
       </c>
       <c r="B32" t="n">
-        <v>57506</v>
+        <v>57491</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4125,16 +4131,16 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -4142,10 +4148,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -4154,13 +4164,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>540220</v>
+        <v>540603</v>
       </c>
       <c r="R32" t="n">
-        <v>7199936</v>
+        <v>7199887</v>
       </c>
       <c r="S32" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4189,7 +4199,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>08:57</t>
+          <t>07:32</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4199,7 +4209,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>08:57</t>
+          <t>07:32</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4226,10 +4236,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123675728</v>
+        <v>123675755</v>
       </c>
       <c r="B33" t="n">
-        <v>56700</v>
+        <v>57644</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4238,31 +4248,35 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4271,10 +4285,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>540526</v>
+        <v>540398</v>
       </c>
       <c r="R33" t="n">
-        <v>7199833</v>
+        <v>7199894</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4306,7 +4320,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4316,7 +4330,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4346,7 +4360,7 @@
         <v>123675722</v>
       </c>
       <c r="B34" t="n">
-        <v>79827</v>
+        <v>79829</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4455,10 +4469,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123675723</v>
+        <v>123675770</v>
       </c>
       <c r="B35" t="n">
-        <v>79896</v>
+        <v>78788</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4467,25 +4481,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4495,10 +4509,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>540541</v>
+        <v>540474</v>
       </c>
       <c r="R35" t="n">
-        <v>7199839</v>
+        <v>7199895</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4530,7 +4544,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4540,7 +4554,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4567,10 +4581,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123675724</v>
+        <v>123675783</v>
       </c>
       <c r="B36" t="n">
-        <v>79903</v>
+        <v>78788</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4579,25 +4593,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4607,10 +4621,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>540524</v>
+        <v>540760</v>
       </c>
       <c r="R36" t="n">
-        <v>7199906</v>
+        <v>7200064</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4642,7 +4656,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4652,7 +4666,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4679,10 +4693,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123675770</v>
+        <v>123675766</v>
       </c>
       <c r="B37" t="n">
-        <v>78786</v>
+        <v>78788</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4719,10 +4733,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>540474</v>
+        <v>540428</v>
       </c>
       <c r="R37" t="n">
-        <v>7199895</v>
+        <v>7199871</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4754,7 +4768,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:23</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4764,7 +4778,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:23</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4794,7 +4808,7 @@
         <v>123675750</v>
       </c>
       <c r="B38" t="n">
-        <v>78786</v>
+        <v>78788</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4903,10 +4917,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123675725</v>
+        <v>123675754</v>
       </c>
       <c r="B39" t="n">
-        <v>78786</v>
+        <v>91008</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4919,21 +4933,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4943,10 +4957,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>540523</v>
+        <v>540318</v>
       </c>
       <c r="R39" t="n">
-        <v>7199906</v>
+        <v>7199932</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4978,7 +4992,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4988,7 +5002,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5015,10 +5029,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123675783</v>
+        <v>123675732</v>
       </c>
       <c r="B40" t="n">
-        <v>78786</v>
+        <v>78788</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5055,10 +5069,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>540760</v>
+        <v>540171</v>
       </c>
       <c r="R40" t="n">
-        <v>7200064</v>
+        <v>7200163</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -5090,7 +5104,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5100,7 +5114,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5127,10 +5141,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123675727</v>
+        <v>123675768</v>
       </c>
       <c r="B41" t="n">
-        <v>56700</v>
+        <v>78788</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5139,43 +5153,38 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>540500</v>
+        <v>540469</v>
       </c>
       <c r="R41" t="n">
-        <v>7199873</v>
+        <v>7199898</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5207,7 +5216,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5217,7 +5226,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5244,10 +5253,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123675755</v>
+        <v>123675725</v>
       </c>
       <c r="B42" t="n">
-        <v>57643</v>
+        <v>78788</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5260,43 +5269,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>540398</v>
+        <v>540523</v>
       </c>
       <c r="R42" t="n">
-        <v>7199894</v>
+        <v>7199906</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5328,7 +5328,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5338,7 +5338,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5365,10 +5365,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123675732</v>
+        <v>123675739</v>
       </c>
       <c r="B43" t="n">
-        <v>78786</v>
+        <v>78788</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5405,10 +5405,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>540171</v>
+        <v>540140</v>
       </c>
       <c r="R43" t="n">
-        <v>7200163</v>
+        <v>7199918</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5440,7 +5440,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5450,7 +5450,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5480,7 +5480,7 @@
         <v>123675730</v>
       </c>
       <c r="B44" t="n">
-        <v>78786</v>
+        <v>78788</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5589,10 +5589,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123675762</v>
+        <v>123675772</v>
       </c>
       <c r="B45" t="n">
-        <v>57506</v>
+        <v>78788</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5605,39 +5605,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>540423</v>
+        <v>540491</v>
       </c>
       <c r="R45" t="n">
-        <v>7199851</v>
+        <v>7199896</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5669,7 +5664,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5679,7 +5674,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5706,10 +5701,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123675772</v>
+        <v>123675749</v>
       </c>
       <c r="B46" t="n">
-        <v>78786</v>
+        <v>57507</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5722,34 +5717,39 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>540491</v>
+        <v>540220</v>
       </c>
       <c r="R46" t="n">
-        <v>7199896</v>
+        <v>7199936</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5781,7 +5781,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>08:57</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5791,7 +5791,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>08:57</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5818,10 +5818,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123675752</v>
+        <v>123675720</v>
       </c>
       <c r="B47" t="n">
-        <v>57490</v>
+        <v>57491</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5863,10 +5863,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>540320</v>
+        <v>540612</v>
       </c>
       <c r="R47" t="n">
-        <v>7199929</v>
+        <v>7199895</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5898,7 +5898,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5908,7 +5908,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD47" t="b">

--- a/artfynd/A 9827-2025 artfynd.xlsx
+++ b/artfynd/A 9827-2025 artfynd.xlsx
@@ -2150,10 +2150,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123675724</v>
+        <v>123675757</v>
       </c>
       <c r="B15" t="n">
-        <v>79905</v>
+        <v>57644</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2162,38 +2162,47 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6464</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>540524</v>
+        <v>540316</v>
       </c>
       <c r="R15" t="n">
-        <v>7199906</v>
+        <v>7200001</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2225,7 +2234,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2235,7 +2244,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2262,10 +2271,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123675763</v>
+        <v>123675780</v>
       </c>
       <c r="B16" t="n">
-        <v>77731</v>
+        <v>58169</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2274,38 +2283,47 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>314</v>
+        <v>103044</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>540425</v>
+        <v>540723</v>
       </c>
       <c r="R16" t="n">
-        <v>7199890</v>
+        <v>7200075</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2337,7 +2355,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>08:27</t>
+          <t>07:29</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2347,7 +2365,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>08:27</t>
+          <t>07:29</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2374,10 +2392,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123675778</v>
+        <v>123675724</v>
       </c>
       <c r="B17" t="n">
-        <v>74879</v>
+        <v>79905</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2386,25 +2404,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6440</v>
+        <v>6464</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2414,10 +2432,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>540666</v>
+        <v>540524</v>
       </c>
       <c r="R17" t="n">
-        <v>7200065</v>
+        <v>7199906</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2449,7 +2467,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>07:38</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2459,7 +2477,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>07:38</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2486,10 +2504,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123675728</v>
+        <v>123675763</v>
       </c>
       <c r="B18" t="n">
-        <v>56700</v>
+        <v>77731</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2498,43 +2516,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100138</v>
+        <v>314</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>540526</v>
+        <v>540425</v>
       </c>
       <c r="R18" t="n">
-        <v>7199833</v>
+        <v>7199890</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2566,7 +2579,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>08:27</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2576,7 +2589,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>08:27</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2603,10 +2616,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123675757</v>
+        <v>123675778</v>
       </c>
       <c r="B19" t="n">
-        <v>57644</v>
+        <v>74879</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2619,43 +2632,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103021</v>
+        <v>6440</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>540316</v>
+        <v>540666</v>
       </c>
       <c r="R19" t="n">
-        <v>7200001</v>
+        <v>7200065</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2687,7 +2691,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>07:38</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2697,7 +2701,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>07:38</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2724,10 +2728,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123675780</v>
+        <v>123675728</v>
       </c>
       <c r="B20" t="n">
-        <v>58169</v>
+        <v>56700</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2740,31 +2744,27 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103044</v>
+        <v>100138</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2773,10 +2773,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>540723</v>
+        <v>540526</v>
       </c>
       <c r="R20" t="n">
-        <v>7200075</v>
+        <v>7199833</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2808,7 +2808,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>07:29</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2818,7 +2818,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>07:29</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3083,10 +3083,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123675781</v>
+        <v>123675774</v>
       </c>
       <c r="B23" t="n">
-        <v>57861</v>
+        <v>78788</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3095,47 +3095,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>540728</v>
+        <v>540546</v>
       </c>
       <c r="R23" t="n">
-        <v>7200067</v>
+        <v>7199996</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3167,7 +3158,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>07:29</t>
+          <t>07:56</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3177,7 +3168,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>07:29</t>
+          <t>07:56</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3204,7 +3195,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123675774</v>
+        <v>123675753</v>
       </c>
       <c r="B24" t="n">
         <v>78788</v>
@@ -3244,10 +3235,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>540546</v>
+        <v>540320</v>
       </c>
       <c r="R24" t="n">
-        <v>7199996</v>
+        <v>7199929</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3279,7 +3270,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>07:56</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3289,7 +3280,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>07:56</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3316,10 +3307,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123675753</v>
+        <v>123675781</v>
       </c>
       <c r="B25" t="n">
-        <v>78788</v>
+        <v>57861</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3328,38 +3319,47 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>540320</v>
+        <v>540728</v>
       </c>
       <c r="R25" t="n">
-        <v>7199929</v>
+        <v>7200067</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3391,7 +3391,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>07:29</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>07:29</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -4115,10 +4115,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123675779</v>
+        <v>123675722</v>
       </c>
       <c r="B32" t="n">
-        <v>57491</v>
+        <v>79829</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4127,50 +4127,41 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>229497</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>540603</v>
+        <v>540541</v>
       </c>
       <c r="R32" t="n">
-        <v>7199887</v>
+        <v>7199839</v>
       </c>
       <c r="S32" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4199,7 +4190,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>07:32</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4209,7 +4200,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>07:32</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4236,10 +4227,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123675755</v>
+        <v>123675779</v>
       </c>
       <c r="B33" t="n">
-        <v>57644</v>
+        <v>57491</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4252,21 +4243,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -4276,7 +4267,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4285,13 +4276,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>540398</v>
+        <v>540603</v>
       </c>
       <c r="R33" t="n">
-        <v>7199894</v>
+        <v>7199887</v>
       </c>
       <c r="S33" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4320,7 +4311,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>07:32</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4330,7 +4321,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>07:32</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4357,10 +4348,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123675722</v>
+        <v>123675755</v>
       </c>
       <c r="B34" t="n">
-        <v>79829</v>
+        <v>57644</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4369,38 +4360,47 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>229497</v>
+        <v>103021</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>540541</v>
+        <v>540398</v>
       </c>
       <c r="R34" t="n">
-        <v>7199839</v>
+        <v>7199894</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4432,7 +4432,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4442,7 +4442,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD34" t="b">

--- a/artfynd/A 9827-2025 artfynd.xlsx
+++ b/artfynd/A 9827-2025 artfynd.xlsx
@@ -2150,10 +2150,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123675757</v>
+        <v>123675763</v>
       </c>
       <c r="B15" t="n">
-        <v>57644</v>
+        <v>77731</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2166,43 +2166,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>314</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Kremp.) A.F.W.Schmidt</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>540316</v>
+        <v>540425</v>
       </c>
       <c r="R15" t="n">
-        <v>7200001</v>
+        <v>7199890</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2234,7 +2225,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>08:27</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2244,7 +2235,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>08:27</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2271,10 +2262,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123675780</v>
+        <v>123675778</v>
       </c>
       <c r="B16" t="n">
-        <v>58169</v>
+        <v>74879</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2283,47 +2274,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103044</v>
+        <v>6440</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>540723</v>
+        <v>540666</v>
       </c>
       <c r="R16" t="n">
-        <v>7200075</v>
+        <v>7200065</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2355,7 +2337,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>07:29</t>
+          <t>07:38</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2365,7 +2347,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>07:29</t>
+          <t>07:38</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2392,10 +2374,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123675724</v>
+        <v>123675728</v>
       </c>
       <c r="B17" t="n">
-        <v>79905</v>
+        <v>56700</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2408,34 +2390,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6464</v>
+        <v>100138</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>540524</v>
+        <v>540526</v>
       </c>
       <c r="R17" t="n">
-        <v>7199906</v>
+        <v>7199833</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2467,7 +2454,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2477,7 +2464,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2504,10 +2491,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123675763</v>
+        <v>123675724</v>
       </c>
       <c r="B18" t="n">
-        <v>77731</v>
+        <v>79905</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2516,25 +2503,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>314</v>
+        <v>6464</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2544,10 +2531,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>540425</v>
+        <v>540524</v>
       </c>
       <c r="R18" t="n">
-        <v>7199890</v>
+        <v>7199906</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2579,7 +2566,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>08:27</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2589,7 +2576,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>08:27</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2616,10 +2603,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123675778</v>
+        <v>123675780</v>
       </c>
       <c r="B19" t="n">
-        <v>74879</v>
+        <v>58169</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2628,38 +2615,47 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6440</v>
+        <v>103044</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>540666</v>
+        <v>540723</v>
       </c>
       <c r="R19" t="n">
-        <v>7200065</v>
+        <v>7200075</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2691,7 +2687,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>07:38</t>
+          <t>07:29</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2701,7 +2697,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>07:38</t>
+          <t>07:29</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2728,10 +2724,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123675728</v>
+        <v>123675759</v>
       </c>
       <c r="B20" t="n">
-        <v>56700</v>
+        <v>57861</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2744,27 +2740,31 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100138</v>
+        <v>103015</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2773,10 +2773,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>540526</v>
+        <v>540345</v>
       </c>
       <c r="R20" t="n">
-        <v>7199833</v>
+        <v>7199934</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2808,7 +2808,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2818,7 +2818,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2845,10 +2845,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123675759</v>
+        <v>123675757</v>
       </c>
       <c r="B21" t="n">
-        <v>57861</v>
+        <v>57644</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2857,30 +2857,30 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2894,10 +2894,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>540345</v>
+        <v>540316</v>
       </c>
       <c r="R21" t="n">
-        <v>7199934</v>
+        <v>7200001</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2929,7 +2929,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2939,7 +2939,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -5477,10 +5477,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123675730</v>
+        <v>123675749</v>
       </c>
       <c r="B44" t="n">
-        <v>78788</v>
+        <v>57507</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5493,34 +5493,39 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>540340</v>
+        <v>540220</v>
       </c>
       <c r="R44" t="n">
-        <v>7200020</v>
+        <v>7199936</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5552,7 +5557,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>08:57</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5562,7 +5567,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>08:57</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5589,10 +5594,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123675772</v>
+        <v>123675720</v>
       </c>
       <c r="B45" t="n">
-        <v>78788</v>
+        <v>57491</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5605,34 +5610,39 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>540491</v>
+        <v>540612</v>
       </c>
       <c r="R45" t="n">
-        <v>7199896</v>
+        <v>7199895</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5664,7 +5674,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5674,7 +5684,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5701,10 +5711,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123675749</v>
+        <v>123675730</v>
       </c>
       <c r="B46" t="n">
-        <v>57507</v>
+        <v>78788</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5717,39 +5727,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>540220</v>
+        <v>540340</v>
       </c>
       <c r="R46" t="n">
-        <v>7199936</v>
+        <v>7200020</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5781,7 +5786,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>08:57</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5791,7 +5796,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>08:57</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5818,10 +5823,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123675720</v>
+        <v>123675772</v>
       </c>
       <c r="B47" t="n">
-        <v>57491</v>
+        <v>78788</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5834,39 +5839,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>540612</v>
+        <v>540491</v>
       </c>
       <c r="R47" t="n">
-        <v>7199895</v>
+        <v>7199896</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5898,7 +5898,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5908,7 +5908,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="AD47" t="b">

--- a/artfynd/A 9827-2025 artfynd.xlsx
+++ b/artfynd/A 9827-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123675737</v>
+        <v>123675779</v>
       </c>
       <c r="B2" t="n">
-        <v>78788</v>
+        <v>57491</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,37 +691,46 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>540120</v>
+        <v>540603</v>
       </c>
       <c r="R2" t="n">
-        <v>7199910</v>
+        <v>7199887</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>07:32</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>07:32</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123675762</v>
+        <v>123675763</v>
       </c>
       <c r="B3" t="n">
-        <v>57507</v>
+        <v>77731</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,39 +812,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>540423</v>
+        <v>540425</v>
       </c>
       <c r="R3" t="n">
-        <v>7199851</v>
+        <v>7199890</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -867,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>08:27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +881,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>08:27</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,10 +908,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123675752</v>
+        <v>123675749</v>
       </c>
       <c r="B4" t="n">
-        <v>57491</v>
+        <v>57507</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,16 +924,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -949,10 +953,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>540320</v>
+        <v>540220</v>
       </c>
       <c r="R4" t="n">
-        <v>7199929</v>
+        <v>7199936</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -984,7 +988,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>08:57</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,7 +998,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>08:57</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,10 +1025,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123675761</v>
+        <v>123675724</v>
       </c>
       <c r="B5" t="n">
-        <v>78788</v>
+        <v>79905</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1033,25 +1037,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1061,10 +1065,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>540369</v>
+        <v>540524</v>
       </c>
       <c r="R5" t="n">
-        <v>7199910</v>
+        <v>7199906</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1096,7 +1100,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>08:37</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1106,7 +1110,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>08:37</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1133,10 +1137,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123675767</v>
+        <v>123675719</v>
       </c>
       <c r="B6" t="n">
-        <v>78874</v>
+        <v>78788</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1145,25 +1149,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6450</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1173,10 +1177,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>540427</v>
+        <v>540622</v>
       </c>
       <c r="R6" t="n">
-        <v>7199883</v>
+        <v>7199937</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1208,7 +1212,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1218,7 +1222,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1245,7 +1249,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123675736</v>
+        <v>123675753</v>
       </c>
       <c r="B7" t="n">
         <v>78788</v>
@@ -1285,10 +1289,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>540078</v>
+        <v>540320</v>
       </c>
       <c r="R7" t="n">
-        <v>7199948</v>
+        <v>7199929</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1320,7 +1324,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1330,7 +1334,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1357,10 +1361,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123675719</v>
+        <v>123675778</v>
       </c>
       <c r="B8" t="n">
-        <v>78788</v>
+        <v>74879</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1373,21 +1377,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1397,10 +1401,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>540622</v>
+        <v>540666</v>
       </c>
       <c r="R8" t="n">
-        <v>7199937</v>
+        <v>7200065</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1432,7 +1436,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>07:38</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1442,7 +1446,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>07:38</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1469,10 +1473,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123675769</v>
+        <v>123675755</v>
       </c>
       <c r="B9" t="n">
-        <v>97369</v>
+        <v>57644</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1481,38 +1485,47 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221945</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>540475</v>
+        <v>540398</v>
       </c>
       <c r="R9" t="n">
-        <v>7199900</v>
+        <v>7199894</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1544,7 +1557,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1554,7 +1567,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1581,10 +1594,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123675723</v>
+        <v>123675783</v>
       </c>
       <c r="B10" t="n">
-        <v>79898</v>
+        <v>78788</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1593,25 +1606,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1621,10 +1634,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>540541</v>
+        <v>540760</v>
       </c>
       <c r="R10" t="n">
-        <v>7199839</v>
+        <v>7200064</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1656,7 +1669,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1666,7 +1679,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1693,10 +1706,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123675738</v>
+        <v>123675771</v>
       </c>
       <c r="B11" t="n">
-        <v>78867</v>
+        <v>57491</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1709,34 +1722,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>864</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>540142</v>
+        <v>540488</v>
       </c>
       <c r="R11" t="n">
-        <v>7199918</v>
+        <v>7199896</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1768,7 +1786,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1778,7 +1796,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1805,10 +1823,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123675756</v>
+        <v>123675767</v>
       </c>
       <c r="B12" t="n">
-        <v>57644</v>
+        <v>78874</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1817,47 +1835,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>6450</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Ach.) Parrique</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>540336</v>
+        <v>540427</v>
       </c>
       <c r="R12" t="n">
-        <v>7199942</v>
+        <v>7199883</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1889,7 +1898,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1899,7 +1908,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1926,10 +1935,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123675764</v>
+        <v>123675725</v>
       </c>
       <c r="B13" t="n">
-        <v>78867</v>
+        <v>78788</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1942,21 +1951,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1966,10 +1975,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>540428</v>
+        <v>540523</v>
       </c>
       <c r="R13" t="n">
-        <v>7199871</v>
+        <v>7199906</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2001,7 +2010,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>08:23</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2011,7 +2020,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>08:23</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2038,10 +2047,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123675751</v>
+        <v>123675762</v>
       </c>
       <c r="B14" t="n">
-        <v>78788</v>
+        <v>57507</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2054,34 +2063,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>540269</v>
+        <v>540423</v>
       </c>
       <c r="R14" t="n">
-        <v>7199949</v>
+        <v>7199851</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2113,7 +2127,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>08:54</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2123,7 +2137,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>08:54</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2150,10 +2164,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123675763</v>
+        <v>123675752</v>
       </c>
       <c r="B15" t="n">
-        <v>77731</v>
+        <v>57491</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2166,34 +2180,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>314</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>540425</v>
+        <v>540320</v>
       </c>
       <c r="R15" t="n">
-        <v>7199890</v>
+        <v>7199929</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2225,7 +2244,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>08:27</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2235,7 +2254,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>08:27</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2262,10 +2281,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123675778</v>
+        <v>123675759</v>
       </c>
       <c r="B16" t="n">
-        <v>74879</v>
+        <v>57861</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2274,38 +2293,47 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6440</v>
+        <v>103015</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>540666</v>
+        <v>540345</v>
       </c>
       <c r="R16" t="n">
-        <v>7200065</v>
+        <v>7199934</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2337,7 +2365,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>07:38</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2347,7 +2375,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>07:38</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2374,10 +2402,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123675728</v>
+        <v>123675775</v>
       </c>
       <c r="B17" t="n">
-        <v>56700</v>
+        <v>82575</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2386,43 +2414,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100138</v>
+        <v>1312</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>540526</v>
+        <v>540545</v>
       </c>
       <c r="R17" t="n">
-        <v>7199833</v>
+        <v>7199990</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2454,7 +2477,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>07:55</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2464,7 +2487,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>07:55</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2491,10 +2514,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123675724</v>
+        <v>123675754</v>
       </c>
       <c r="B18" t="n">
-        <v>79905</v>
+        <v>91008</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2503,25 +2526,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6464</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2531,10 +2554,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>540524</v>
+        <v>540318</v>
       </c>
       <c r="R18" t="n">
-        <v>7199906</v>
+        <v>7199932</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2566,7 +2589,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2576,7 +2599,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2603,10 +2626,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123675780</v>
+        <v>123675732</v>
       </c>
       <c r="B19" t="n">
-        <v>58169</v>
+        <v>78788</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2615,47 +2638,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103044</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>540723</v>
+        <v>540171</v>
       </c>
       <c r="R19" t="n">
-        <v>7200075</v>
+        <v>7200163</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2687,7 +2701,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>07:29</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2697,7 +2711,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>07:29</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2724,10 +2738,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123675759</v>
+        <v>123675756</v>
       </c>
       <c r="B20" t="n">
-        <v>57861</v>
+        <v>57644</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2736,30 +2750,30 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2773,10 +2787,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>540345</v>
+        <v>540336</v>
       </c>
       <c r="R20" t="n">
-        <v>7199934</v>
+        <v>7199942</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2808,7 +2822,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2818,7 +2832,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2845,10 +2859,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123675757</v>
+        <v>123675761</v>
       </c>
       <c r="B21" t="n">
-        <v>57644</v>
+        <v>78788</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2861,43 +2875,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>540316</v>
+        <v>540369</v>
       </c>
       <c r="R21" t="n">
-        <v>7200001</v>
+        <v>7199910</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2929,7 +2934,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>08:37</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2939,7 +2944,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>08:37</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2966,10 +2971,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123675727</v>
+        <v>123675730</v>
       </c>
       <c r="B22" t="n">
-        <v>56700</v>
+        <v>78788</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2978,43 +2983,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>540500</v>
+        <v>540340</v>
       </c>
       <c r="R22" t="n">
-        <v>7199873</v>
+        <v>7200020</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3046,7 +3046,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3056,7 +3056,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3083,10 +3083,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123675774</v>
+        <v>123675727</v>
       </c>
       <c r="B23" t="n">
-        <v>78788</v>
+        <v>56700</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3095,38 +3095,43 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>540546</v>
+        <v>540500</v>
       </c>
       <c r="R23" t="n">
-        <v>7199996</v>
+        <v>7199873</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3158,7 +3163,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>07:56</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3168,7 +3173,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>07:56</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3195,10 +3200,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123675753</v>
+        <v>123675726</v>
       </c>
       <c r="B24" t="n">
-        <v>78788</v>
+        <v>79898</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3207,25 +3212,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3235,10 +3240,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>540320</v>
+        <v>540524</v>
       </c>
       <c r="R24" t="n">
-        <v>7199929</v>
+        <v>7199907</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3270,7 +3275,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3280,7 +3285,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3307,10 +3312,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123675781</v>
+        <v>123675751</v>
       </c>
       <c r="B25" t="n">
-        <v>57861</v>
+        <v>78788</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3319,47 +3324,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>540728</v>
+        <v>540269</v>
       </c>
       <c r="R25" t="n">
-        <v>7200067</v>
+        <v>7199949</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3391,7 +3387,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>07:29</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3401,7 +3397,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>07:29</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3428,10 +3424,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123675773</v>
+        <v>123675735</v>
       </c>
       <c r="B26" t="n">
-        <v>79898</v>
+        <v>57491</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3440,38 +3436,43 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>540495</v>
+        <v>540080</v>
       </c>
       <c r="R26" t="n">
-        <v>7199932</v>
+        <v>7199959</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3503,7 +3504,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>08:03</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3513,7 +3514,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>08:03</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3540,10 +3541,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123675735</v>
+        <v>123675772</v>
       </c>
       <c r="B27" t="n">
-        <v>57491</v>
+        <v>78788</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3556,39 +3557,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>540080</v>
+        <v>540491</v>
       </c>
       <c r="R27" t="n">
-        <v>7199959</v>
+        <v>7199896</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3620,7 +3616,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3630,7 +3626,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3657,10 +3653,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123675771</v>
+        <v>123675739</v>
       </c>
       <c r="B28" t="n">
-        <v>57491</v>
+        <v>78788</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3673,39 +3669,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>540488</v>
+        <v>540140</v>
       </c>
       <c r="R28" t="n">
-        <v>7199896</v>
+        <v>7199918</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3737,7 +3728,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3747,7 +3738,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3774,7 +3765,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123675726</v>
+        <v>123675723</v>
       </c>
       <c r="B29" t="n">
         <v>79898</v>
@@ -3814,10 +3805,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>540524</v>
+        <v>540541</v>
       </c>
       <c r="R29" t="n">
-        <v>7199907</v>
+        <v>7199839</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3849,7 +3840,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3859,7 +3850,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3886,10 +3877,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123675718</v>
+        <v>123675738</v>
       </c>
       <c r="B30" t="n">
-        <v>56700</v>
+        <v>78867</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3898,43 +3889,38 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100138</v>
+        <v>864</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>540623</v>
+        <v>540142</v>
       </c>
       <c r="R30" t="n">
-        <v>7199942</v>
+        <v>7199918</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3966,7 +3952,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3976,7 +3962,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4003,10 +3989,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123675775</v>
+        <v>123675773</v>
       </c>
       <c r="B31" t="n">
-        <v>82575</v>
+        <v>79898</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4015,25 +4001,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1312</v>
+        <v>6462</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4043,10 +4029,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>540545</v>
+        <v>540495</v>
       </c>
       <c r="R31" t="n">
-        <v>7199990</v>
+        <v>7199932</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4078,7 +4064,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>07:55</t>
+          <t>08:03</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4088,7 +4074,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>07:55</t>
+          <t>08:03</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4115,10 +4101,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123675722</v>
+        <v>123675736</v>
       </c>
       <c r="B32" t="n">
-        <v>79829</v>
+        <v>78788</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4127,25 +4113,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4155,10 +4141,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>540541</v>
+        <v>540078</v>
       </c>
       <c r="R32" t="n">
-        <v>7199839</v>
+        <v>7199948</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4190,7 +4176,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4200,7 +4186,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4227,7 +4213,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123675779</v>
+        <v>123675720</v>
       </c>
       <c r="B33" t="n">
         <v>57491</v>
@@ -4260,14 +4246,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4276,13 +4258,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>540603</v>
+        <v>540612</v>
       </c>
       <c r="R33" t="n">
-        <v>7199887</v>
+        <v>7199895</v>
       </c>
       <c r="S33" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4311,7 +4293,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>07:32</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4321,7 +4303,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>07:32</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4348,7 +4330,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123675755</v>
+        <v>123675757</v>
       </c>
       <c r="B34" t="n">
         <v>57644</v>
@@ -4397,10 +4379,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>540398</v>
+        <v>540316</v>
       </c>
       <c r="R34" t="n">
-        <v>7199894</v>
+        <v>7200001</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4469,10 +4451,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123675770</v>
+        <v>123675722</v>
       </c>
       <c r="B35" t="n">
-        <v>78788</v>
+        <v>79829</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4481,25 +4463,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4509,10 +4491,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>540474</v>
+        <v>540541</v>
       </c>
       <c r="R35" t="n">
-        <v>7199895</v>
+        <v>7199839</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4544,7 +4526,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4554,7 +4536,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4581,7 +4563,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123675783</v>
+        <v>123675750</v>
       </c>
       <c r="B36" t="n">
         <v>78788</v>
@@ -4621,10 +4603,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>540760</v>
+        <v>540220</v>
       </c>
       <c r="R36" t="n">
-        <v>7200064</v>
+        <v>7199934</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4656,7 +4638,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:57</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4666,7 +4648,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:57</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4693,7 +4675,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123675766</v>
+        <v>123675774</v>
       </c>
       <c r="B37" t="n">
         <v>78788</v>
@@ -4733,10 +4715,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>540428</v>
+        <v>540546</v>
       </c>
       <c r="R37" t="n">
-        <v>7199871</v>
+        <v>7199996</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4768,7 +4750,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>08:23</t>
+          <t>07:56</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4778,7 +4760,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>08:23</t>
+          <t>07:56</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4805,10 +4787,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123675750</v>
+        <v>123675769</v>
       </c>
       <c r="B38" t="n">
-        <v>78788</v>
+        <v>96957</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4817,25 +4799,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4845,10 +4827,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>540220</v>
+        <v>540475</v>
       </c>
       <c r="R38" t="n">
-        <v>7199934</v>
+        <v>7199900</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4880,7 +4862,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>08:57</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4890,7 +4872,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>08:57</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4917,10 +4899,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123675754</v>
+        <v>123675768</v>
       </c>
       <c r="B39" t="n">
-        <v>91008</v>
+        <v>78788</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4933,21 +4915,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4957,10 +4939,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>540318</v>
+        <v>540469</v>
       </c>
       <c r="R39" t="n">
-        <v>7199932</v>
+        <v>7199898</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4992,7 +4974,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5002,7 +4984,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5029,10 +5011,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123675732</v>
+        <v>123675728</v>
       </c>
       <c r="B40" t="n">
-        <v>78788</v>
+        <v>56700</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5041,38 +5023,43 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>540171</v>
+        <v>540526</v>
       </c>
       <c r="R40" t="n">
-        <v>7200163</v>
+        <v>7199833</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -5104,7 +5091,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5114,7 +5101,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5141,7 +5128,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123675768</v>
+        <v>123675770</v>
       </c>
       <c r="B41" t="n">
         <v>78788</v>
@@ -5181,10 +5168,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>540469</v>
+        <v>540474</v>
       </c>
       <c r="R41" t="n">
-        <v>7199898</v>
+        <v>7199895</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5216,7 +5203,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5226,7 +5213,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5253,10 +5240,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123675725</v>
+        <v>123675764</v>
       </c>
       <c r="B42" t="n">
-        <v>78788</v>
+        <v>78867</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5269,21 +5256,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5293,10 +5280,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>540523</v>
+        <v>540428</v>
       </c>
       <c r="R42" t="n">
-        <v>7199906</v>
+        <v>7199871</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5328,7 +5315,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>08:23</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5338,7 +5325,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>08:23</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5365,10 +5352,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123675739</v>
+        <v>123675780</v>
       </c>
       <c r="B43" t="n">
-        <v>78788</v>
+        <v>58169</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5377,38 +5364,47 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>103044</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>540140</v>
+        <v>540723</v>
       </c>
       <c r="R43" t="n">
-        <v>7199918</v>
+        <v>7200075</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5440,7 +5436,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>07:29</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5450,7 +5446,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>07:29</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5477,10 +5473,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123675749</v>
+        <v>123675766</v>
       </c>
       <c r="B44" t="n">
-        <v>57507</v>
+        <v>78788</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5493,39 +5489,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>540220</v>
+        <v>540428</v>
       </c>
       <c r="R44" t="n">
-        <v>7199936</v>
+        <v>7199871</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5557,7 +5548,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>08:57</t>
+          <t>08:23</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5567,7 +5558,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>08:57</t>
+          <t>08:23</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5594,10 +5585,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123675720</v>
+        <v>123675737</v>
       </c>
       <c r="B45" t="n">
-        <v>57491</v>
+        <v>78788</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5610,39 +5601,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>540612</v>
+        <v>540120</v>
       </c>
       <c r="R45" t="n">
-        <v>7199895</v>
+        <v>7199910</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5674,7 +5660,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5684,7 +5670,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5711,10 +5697,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123675730</v>
+        <v>123675718</v>
       </c>
       <c r="B46" t="n">
-        <v>78788</v>
+        <v>56700</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5723,38 +5709,43 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>540340</v>
+        <v>540623</v>
       </c>
       <c r="R46" t="n">
-        <v>7200020</v>
+        <v>7199942</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5786,7 +5777,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5796,7 +5787,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5823,10 +5814,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123675772</v>
+        <v>123675781</v>
       </c>
       <c r="B47" t="n">
-        <v>78788</v>
+        <v>57861</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5835,38 +5826,47 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>540491</v>
+        <v>540728</v>
       </c>
       <c r="R47" t="n">
-        <v>7199896</v>
+        <v>7200067</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5898,7 +5898,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:29</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5908,7 +5908,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:29</t>
         </is>
       </c>
       <c r="AD47" t="b">

--- a/artfynd/A 9827-2025 artfynd.xlsx
+++ b/artfynd/A 9827-2025 artfynd.xlsx
@@ -908,10 +908,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123675749</v>
+        <v>123675724</v>
       </c>
       <c r="B4" t="n">
-        <v>57507</v>
+        <v>79905</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,43 +920,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>6464</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>540220</v>
+        <v>540524</v>
       </c>
       <c r="R4" t="n">
-        <v>7199936</v>
+        <v>7199906</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -988,7 +983,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>08:57</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -998,7 +993,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>08:57</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1025,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123675724</v>
+        <v>123675749</v>
       </c>
       <c r="B5" t="n">
-        <v>79905</v>
+        <v>57507</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1037,38 +1032,43 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6464</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>540524</v>
+        <v>540220</v>
       </c>
       <c r="R5" t="n">
-        <v>7199906</v>
+        <v>7199936</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>08:57</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1110,7 +1110,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>08:57</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1594,10 +1594,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123675783</v>
+        <v>123675771</v>
       </c>
       <c r="B10" t="n">
-        <v>78788</v>
+        <v>57491</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1610,34 +1610,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>540760</v>
+        <v>540488</v>
       </c>
       <c r="R10" t="n">
-        <v>7200064</v>
+        <v>7199896</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1669,7 +1674,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1679,7 +1684,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1706,10 +1711,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123675771</v>
+        <v>123675783</v>
       </c>
       <c r="B11" t="n">
-        <v>57491</v>
+        <v>78788</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1722,39 +1727,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>540488</v>
+        <v>540760</v>
       </c>
       <c r="R11" t="n">
-        <v>7199896</v>
+        <v>7200064</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1786,7 +1786,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2402,10 +2402,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123675775</v>
+        <v>123675756</v>
       </c>
       <c r="B17" t="n">
-        <v>82575</v>
+        <v>57644</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2418,34 +2418,43 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1312</v>
+        <v>103021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>540545</v>
+        <v>540336</v>
       </c>
       <c r="R17" t="n">
-        <v>7199990</v>
+        <v>7199942</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2477,7 +2486,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>07:55</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2487,7 +2496,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>07:55</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2514,10 +2523,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123675754</v>
+        <v>123675775</v>
       </c>
       <c r="B18" t="n">
-        <v>91008</v>
+        <v>82575</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2530,21 +2539,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2554,10 +2563,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>540318</v>
+        <v>540545</v>
       </c>
       <c r="R18" t="n">
-        <v>7199932</v>
+        <v>7199990</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2589,7 +2598,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>07:55</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2599,7 +2608,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>07:55</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2626,10 +2635,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123675732</v>
+        <v>123675754</v>
       </c>
       <c r="B19" t="n">
-        <v>78788</v>
+        <v>91008</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2642,21 +2651,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2666,10 +2675,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>540171</v>
+        <v>540318</v>
       </c>
       <c r="R19" t="n">
-        <v>7200163</v>
+        <v>7199932</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2701,7 +2710,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2711,7 +2720,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2738,10 +2747,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123675756</v>
+        <v>123675732</v>
       </c>
       <c r="B20" t="n">
-        <v>57644</v>
+        <v>78788</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2754,43 +2763,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>540336</v>
+        <v>540171</v>
       </c>
       <c r="R20" t="n">
-        <v>7199942</v>
+        <v>7200163</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2822,7 +2822,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2832,7 +2832,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -5352,10 +5352,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123675780</v>
+        <v>123675766</v>
       </c>
       <c r="B43" t="n">
-        <v>58169</v>
+        <v>78788</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5364,47 +5364,38 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>103044</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>540723</v>
+        <v>540428</v>
       </c>
       <c r="R43" t="n">
-        <v>7200075</v>
+        <v>7199871</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5436,7 +5427,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>07:29</t>
+          <t>08:23</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5446,7 +5437,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>07:29</t>
+          <t>08:23</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5473,10 +5464,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123675766</v>
+        <v>123675780</v>
       </c>
       <c r="B44" t="n">
-        <v>78788</v>
+        <v>58169</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5485,38 +5476,47 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>103044</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>540428</v>
+        <v>540723</v>
       </c>
       <c r="R44" t="n">
-        <v>7199871</v>
+        <v>7200075</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5548,7 +5548,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>08:23</t>
+          <t>07:29</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5558,7 +5558,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>08:23</t>
+          <t>07:29</t>
         </is>
       </c>
       <c r="AD44" t="b">

--- a/artfynd/A 9827-2025 artfynd.xlsx
+++ b/artfynd/A 9827-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123675779</v>
+        <v>123675778</v>
       </c>
       <c r="B2" t="n">
-        <v>57491</v>
+        <v>74879</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,46 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>540603</v>
+        <v>540666</v>
       </c>
       <c r="R2" t="n">
-        <v>7199887</v>
+        <v>7200065</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>07:32</t>
+          <t>07:38</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>07:32</t>
+          <t>07:38</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123675763</v>
+        <v>123675738</v>
       </c>
       <c r="B3" t="n">
-        <v>77731</v>
+        <v>78867</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -812,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>314</v>
+        <v>864</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -836,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>540425</v>
+        <v>540142</v>
       </c>
       <c r="R3" t="n">
-        <v>7199890</v>
+        <v>7199918</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -871,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>08:27</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>08:27</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123675724</v>
+        <v>123675754</v>
       </c>
       <c r="B4" t="n">
-        <v>79905</v>
+        <v>91008</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,25 +911,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6464</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -948,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>540524</v>
+        <v>540318</v>
       </c>
       <c r="R4" t="n">
-        <v>7199906</v>
+        <v>7199932</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -983,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -993,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1020,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123675749</v>
+        <v>123675766</v>
       </c>
       <c r="B5" t="n">
-        <v>57507</v>
+        <v>78788</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,39 +1027,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>540220</v>
+        <v>540428</v>
       </c>
       <c r="R5" t="n">
-        <v>7199936</v>
+        <v>7199871</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1100,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>08:57</t>
+          <t>08:23</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1110,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>08:57</t>
+          <t>08:23</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1137,7 +1123,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123675719</v>
+        <v>123675730</v>
       </c>
       <c r="B6" t="n">
         <v>78788</v>
@@ -1177,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>540622</v>
+        <v>540340</v>
       </c>
       <c r="R6" t="n">
-        <v>7199937</v>
+        <v>7200020</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1212,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1222,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1249,7 +1235,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123675753</v>
+        <v>123675732</v>
       </c>
       <c r="B7" t="n">
         <v>78788</v>
@@ -1289,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>540320</v>
+        <v>540171</v>
       </c>
       <c r="R7" t="n">
-        <v>7199929</v>
+        <v>7200163</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1324,7 +1310,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1334,7 +1320,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1361,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123675778</v>
+        <v>123675764</v>
       </c>
       <c r="B8" t="n">
-        <v>74879</v>
+        <v>78867</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1377,21 +1363,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6440</v>
+        <v>864</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1401,10 +1387,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>540666</v>
+        <v>540428</v>
       </c>
       <c r="R8" t="n">
-        <v>7200065</v>
+        <v>7199871</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1436,7 +1422,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>07:38</t>
+          <t>08:23</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1446,7 +1432,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>07:38</t>
+          <t>08:23</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1473,10 +1459,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123675755</v>
+        <v>123675724</v>
       </c>
       <c r="B9" t="n">
-        <v>57644</v>
+        <v>79905</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1485,47 +1471,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>6464</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>540398</v>
+        <v>540524</v>
       </c>
       <c r="R9" t="n">
-        <v>7199894</v>
+        <v>7199906</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1557,7 +1534,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1567,7 +1544,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1594,10 +1571,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123675771</v>
+        <v>123675728</v>
       </c>
       <c r="B10" t="n">
-        <v>57491</v>
+        <v>56700</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1606,31 +1583,31 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1639,10 +1616,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>540488</v>
+        <v>540526</v>
       </c>
       <c r="R10" t="n">
-        <v>7199896</v>
+        <v>7199833</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1674,7 +1651,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1684,7 +1661,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1711,7 +1688,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123675783</v>
+        <v>123675761</v>
       </c>
       <c r="B11" t="n">
         <v>78788</v>
@@ -1751,10 +1728,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>540760</v>
+        <v>540369</v>
       </c>
       <c r="R11" t="n">
-        <v>7200064</v>
+        <v>7199910</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1786,7 +1763,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:37</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1796,7 +1773,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:37</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1823,10 +1800,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123675767</v>
+        <v>123675719</v>
       </c>
       <c r="B12" t="n">
-        <v>78874</v>
+        <v>78788</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1835,25 +1812,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6450</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1863,10 +1840,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>540427</v>
+        <v>540622</v>
       </c>
       <c r="R12" t="n">
-        <v>7199883</v>
+        <v>7199937</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1898,7 +1875,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1908,7 +1885,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1935,10 +1912,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123675725</v>
+        <v>123675726</v>
       </c>
       <c r="B13" t="n">
-        <v>78788</v>
+        <v>79898</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1947,25 +1924,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1975,10 +1952,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>540523</v>
+        <v>540524</v>
       </c>
       <c r="R13" t="n">
-        <v>7199906</v>
+        <v>7199907</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2047,10 +2024,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123675762</v>
+        <v>123675769</v>
       </c>
       <c r="B14" t="n">
-        <v>57507</v>
+        <v>96957</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2059,43 +2036,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>540423</v>
+        <v>540475</v>
       </c>
       <c r="R14" t="n">
-        <v>7199851</v>
+        <v>7199900</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2127,7 +2099,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2137,7 +2109,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2164,10 +2136,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123675752</v>
+        <v>123675767</v>
       </c>
       <c r="B15" t="n">
-        <v>57491</v>
+        <v>78874</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2176,43 +2148,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6450</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>540320</v>
+        <v>540427</v>
       </c>
       <c r="R15" t="n">
-        <v>7199929</v>
+        <v>7199883</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2244,7 +2211,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2254,7 +2221,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2281,10 +2248,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123675759</v>
+        <v>123675727</v>
       </c>
       <c r="B16" t="n">
-        <v>57861</v>
+        <v>56700</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2297,31 +2264,27 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103015</v>
+        <v>100138</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2330,10 +2293,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>540345</v>
+        <v>540500</v>
       </c>
       <c r="R16" t="n">
-        <v>7199934</v>
+        <v>7199873</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2365,7 +2328,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2375,7 +2338,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2402,10 +2365,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123675756</v>
+        <v>123675771</v>
       </c>
       <c r="B17" t="n">
-        <v>57644</v>
+        <v>57491</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2418,31 +2381,27 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2451,10 +2410,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>540336</v>
+        <v>540488</v>
       </c>
       <c r="R17" t="n">
-        <v>7199942</v>
+        <v>7199896</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2486,7 +2445,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2496,7 +2455,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2523,10 +2482,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123675775</v>
+        <v>123675779</v>
       </c>
       <c r="B18" t="n">
-        <v>82575</v>
+        <v>57491</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2539,37 +2498,46 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>540545</v>
+        <v>540603</v>
       </c>
       <c r="R18" t="n">
-        <v>7199990</v>
+        <v>7199887</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2598,7 +2566,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>07:55</t>
+          <t>07:32</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2608,7 +2576,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>07:55</t>
+          <t>07:32</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2635,10 +2603,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123675754</v>
+        <v>123675722</v>
       </c>
       <c r="B19" t="n">
-        <v>91008</v>
+        <v>79829</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2647,25 +2615,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>229497</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2675,10 +2643,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>540318</v>
+        <v>540541</v>
       </c>
       <c r="R19" t="n">
-        <v>7199932</v>
+        <v>7199839</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2710,7 +2678,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2720,7 +2688,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2747,7 +2715,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123675732</v>
+        <v>123675753</v>
       </c>
       <c r="B20" t="n">
         <v>78788</v>
@@ -2787,10 +2755,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>540171</v>
+        <v>540320</v>
       </c>
       <c r="R20" t="n">
-        <v>7200163</v>
+        <v>7199929</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2822,7 +2790,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2832,7 +2800,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2859,10 +2827,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123675761</v>
+        <v>123675773</v>
       </c>
       <c r="B21" t="n">
-        <v>78788</v>
+        <v>79898</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2871,25 +2839,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2899,10 +2867,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>540369</v>
+        <v>540495</v>
       </c>
       <c r="R21" t="n">
-        <v>7199910</v>
+        <v>7199932</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2934,7 +2902,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>08:37</t>
+          <t>08:03</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2944,7 +2912,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>08:37</t>
+          <t>08:03</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2971,7 +2939,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123675730</v>
+        <v>123675750</v>
       </c>
       <c r="B22" t="n">
         <v>78788</v>
@@ -3011,10 +2979,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>540340</v>
+        <v>540220</v>
       </c>
       <c r="R22" t="n">
-        <v>7200020</v>
+        <v>7199934</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3046,7 +3014,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>08:57</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3056,7 +3024,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>08:57</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3083,10 +3051,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123675727</v>
+        <v>123675736</v>
       </c>
       <c r="B23" t="n">
-        <v>56700</v>
+        <v>78788</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3095,43 +3063,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>540500</v>
+        <v>540078</v>
       </c>
       <c r="R23" t="n">
-        <v>7199873</v>
+        <v>7199948</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3163,7 +3126,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3173,7 +3136,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3200,10 +3163,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123675726</v>
+        <v>123675725</v>
       </c>
       <c r="B24" t="n">
-        <v>79898</v>
+        <v>78788</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3212,25 +3175,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3240,10 +3203,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>540524</v>
+        <v>540523</v>
       </c>
       <c r="R24" t="n">
-        <v>7199907</v>
+        <v>7199906</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3312,10 +3275,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123675751</v>
+        <v>123675735</v>
       </c>
       <c r="B25" t="n">
-        <v>78788</v>
+        <v>57491</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3328,34 +3291,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>540269</v>
+        <v>540080</v>
       </c>
       <c r="R25" t="n">
-        <v>7199949</v>
+        <v>7199959</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3387,7 +3355,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>08:54</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3397,7 +3365,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>08:54</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3424,10 +3392,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123675735</v>
+        <v>123675718</v>
       </c>
       <c r="B26" t="n">
-        <v>57491</v>
+        <v>56700</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3436,31 +3404,31 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3469,10 +3437,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>540080</v>
+        <v>540623</v>
       </c>
       <c r="R26" t="n">
-        <v>7199959</v>
+        <v>7199942</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3504,7 +3472,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3514,7 +3482,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3541,10 +3509,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123675772</v>
+        <v>123675755</v>
       </c>
       <c r="B27" t="n">
-        <v>78788</v>
+        <v>57644</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3557,34 +3525,43 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>540491</v>
+        <v>540398</v>
       </c>
       <c r="R27" t="n">
-        <v>7199896</v>
+        <v>7199894</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3616,7 +3593,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3626,7 +3603,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3653,10 +3630,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123675739</v>
+        <v>123675749</v>
       </c>
       <c r="B28" t="n">
-        <v>78788</v>
+        <v>57507</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3669,34 +3646,39 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>540140</v>
+        <v>540220</v>
       </c>
       <c r="R28" t="n">
-        <v>7199918</v>
+        <v>7199936</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3728,7 +3710,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>08:57</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3738,7 +3720,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>08:57</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3765,10 +3747,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123675723</v>
+        <v>123675752</v>
       </c>
       <c r="B29" t="n">
-        <v>79898</v>
+        <v>57491</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3777,38 +3759,43 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>540541</v>
+        <v>540320</v>
       </c>
       <c r="R29" t="n">
-        <v>7199839</v>
+        <v>7199929</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3840,7 +3827,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3850,7 +3837,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3877,10 +3864,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123675738</v>
+        <v>123675780</v>
       </c>
       <c r="B30" t="n">
-        <v>78867</v>
+        <v>58169</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3889,38 +3876,47 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>864</v>
+        <v>103044</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>540142</v>
+        <v>540723</v>
       </c>
       <c r="R30" t="n">
-        <v>7199918</v>
+        <v>7200075</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3952,7 +3948,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>07:29</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3962,7 +3958,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>07:29</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3989,10 +3985,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123675773</v>
+        <v>123675775</v>
       </c>
       <c r="B31" t="n">
-        <v>79898</v>
+        <v>82575</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4001,25 +3997,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6462</v>
+        <v>1312</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4029,10 +4025,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>540495</v>
+        <v>540545</v>
       </c>
       <c r="R31" t="n">
-        <v>7199932</v>
+        <v>7199990</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4064,7 +4060,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>08:03</t>
+          <t>07:55</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4074,7 +4070,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>08:03</t>
+          <t>07:55</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4101,10 +4097,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123675736</v>
+        <v>123675757</v>
       </c>
       <c r="B32" t="n">
-        <v>78788</v>
+        <v>57644</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4117,34 +4113,43 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>540078</v>
+        <v>540316</v>
       </c>
       <c r="R32" t="n">
-        <v>7199948</v>
+        <v>7200001</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4176,7 +4181,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4186,7 +4191,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4213,10 +4218,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123675720</v>
+        <v>123675763</v>
       </c>
       <c r="B33" t="n">
-        <v>57491</v>
+        <v>77731</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4229,39 +4234,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>314</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>540612</v>
+        <v>540425</v>
       </c>
       <c r="R33" t="n">
-        <v>7199895</v>
+        <v>7199890</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>08:27</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4303,7 +4303,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>08:27</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4330,10 +4330,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123675757</v>
+        <v>123675783</v>
       </c>
       <c r="B34" t="n">
-        <v>57644</v>
+        <v>78788</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4346,43 +4346,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>540316</v>
+        <v>540760</v>
       </c>
       <c r="R34" t="n">
-        <v>7200001</v>
+        <v>7200064</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4414,7 +4405,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4424,7 +4415,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4451,10 +4442,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123675722</v>
+        <v>123675751</v>
       </c>
       <c r="B35" t="n">
-        <v>79829</v>
+        <v>78788</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4463,25 +4454,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4491,10 +4482,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>540541</v>
+        <v>540269</v>
       </c>
       <c r="R35" t="n">
-        <v>7199839</v>
+        <v>7199949</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4526,7 +4517,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4536,7 +4527,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4563,10 +4554,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123675750</v>
+        <v>123675759</v>
       </c>
       <c r="B36" t="n">
-        <v>78788</v>
+        <v>57861</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4575,35 +4566,44 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>540220</v>
+        <v>540345</v>
       </c>
       <c r="R36" t="n">
         <v>7199934</v>
@@ -4638,7 +4638,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>08:57</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4648,7 +4648,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>08:57</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4675,10 +4675,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123675774</v>
+        <v>123675762</v>
       </c>
       <c r="B37" t="n">
-        <v>78788</v>
+        <v>57507</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4691,34 +4691,39 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>540546</v>
+        <v>540423</v>
       </c>
       <c r="R37" t="n">
-        <v>7199996</v>
+        <v>7199851</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4750,7 +4755,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>07:56</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4760,7 +4765,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>07:56</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4787,10 +4792,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123675769</v>
+        <v>123675720</v>
       </c>
       <c r="B38" t="n">
-        <v>96957</v>
+        <v>57491</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4799,38 +4804,43 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>540475</v>
+        <v>540612</v>
       </c>
       <c r="R38" t="n">
-        <v>7199900</v>
+        <v>7199895</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4862,7 +4872,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4872,7 +4882,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4899,10 +4909,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123675768</v>
+        <v>123675781</v>
       </c>
       <c r="B39" t="n">
-        <v>78788</v>
+        <v>57861</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4911,38 +4921,47 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>540469</v>
+        <v>540728</v>
       </c>
       <c r="R39" t="n">
-        <v>7199898</v>
+        <v>7200067</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4974,7 +4993,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>07:29</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4984,7 +5003,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>07:29</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5011,10 +5030,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123675728</v>
+        <v>123675723</v>
       </c>
       <c r="B40" t="n">
-        <v>56700</v>
+        <v>79898</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5027,39 +5046,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100138</v>
+        <v>6462</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>540526</v>
+        <v>540541</v>
       </c>
       <c r="R40" t="n">
-        <v>7199833</v>
+        <v>7199839</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -5091,7 +5105,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5101,7 +5115,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5128,7 +5142,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123675770</v>
+        <v>123675739</v>
       </c>
       <c r="B41" t="n">
         <v>78788</v>
@@ -5168,10 +5182,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>540474</v>
+        <v>540140</v>
       </c>
       <c r="R41" t="n">
-        <v>7199895</v>
+        <v>7199918</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5203,7 +5217,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5213,7 +5227,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5240,10 +5254,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123675764</v>
+        <v>123675768</v>
       </c>
       <c r="B42" t="n">
-        <v>78867</v>
+        <v>78788</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5256,21 +5270,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5280,10 +5294,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>540428</v>
+        <v>540469</v>
       </c>
       <c r="R42" t="n">
-        <v>7199871</v>
+        <v>7199898</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5315,7 +5329,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>08:23</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5325,7 +5339,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>08:23</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5352,7 +5366,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123675766</v>
+        <v>123675774</v>
       </c>
       <c r="B43" t="n">
         <v>78788</v>
@@ -5392,10 +5406,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>540428</v>
+        <v>540546</v>
       </c>
       <c r="R43" t="n">
-        <v>7199871</v>
+        <v>7199996</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5427,7 +5441,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>08:23</t>
+          <t>07:56</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5437,7 +5451,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>08:23</t>
+          <t>07:56</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5464,10 +5478,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123675780</v>
+        <v>123675770</v>
       </c>
       <c r="B44" t="n">
-        <v>58169</v>
+        <v>78788</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5476,47 +5490,38 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>103044</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>540723</v>
+        <v>540474</v>
       </c>
       <c r="R44" t="n">
-        <v>7200075</v>
+        <v>7199895</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5548,7 +5553,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>07:29</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5558,7 +5563,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>07:29</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5697,10 +5702,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123675718</v>
+        <v>123675772</v>
       </c>
       <c r="B46" t="n">
-        <v>56700</v>
+        <v>78788</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5709,43 +5714,38 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>540623</v>
+        <v>540491</v>
       </c>
       <c r="R46" t="n">
-        <v>7199942</v>
+        <v>7199896</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5777,7 +5777,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5787,7 +5787,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5814,10 +5814,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123675781</v>
+        <v>123675756</v>
       </c>
       <c r="B47" t="n">
-        <v>57861</v>
+        <v>57644</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5826,25 +5826,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -5863,10 +5863,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>540728</v>
+        <v>540336</v>
       </c>
       <c r="R47" t="n">
-        <v>7200067</v>
+        <v>7199942</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5898,7 +5898,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>07:29</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5908,7 +5908,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>07:29</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD47" t="b">

--- a/artfynd/A 9827-2025 artfynd.xlsx
+++ b/artfynd/A 9827-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123675778</v>
+        <v>123675762</v>
       </c>
       <c r="B2" t="n">
-        <v>74879</v>
+        <v>57507</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6440</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>540666</v>
+        <v>540423</v>
       </c>
       <c r="R2" t="n">
-        <v>7200065</v>
+        <v>7199851</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>07:38</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>07:38</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123675738</v>
+        <v>123675772</v>
       </c>
       <c r="B3" t="n">
-        <v>78867</v>
+        <v>78788</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +808,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>540142</v>
+        <v>540491</v>
       </c>
       <c r="R3" t="n">
-        <v>7199918</v>
+        <v>7199896</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123675754</v>
+        <v>123675739</v>
       </c>
       <c r="B4" t="n">
-        <v>91008</v>
+        <v>78788</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,21 +920,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +944,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>540318</v>
+        <v>540140</v>
       </c>
       <c r="R4" t="n">
-        <v>7199932</v>
+        <v>7199918</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -974,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123675766</v>
+        <v>123675759</v>
       </c>
       <c r="B5" t="n">
-        <v>78788</v>
+        <v>57861</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,38 +1028,47 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>540428</v>
+        <v>540345</v>
       </c>
       <c r="R5" t="n">
-        <v>7199871</v>
+        <v>7199934</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1086,7 +1100,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>08:23</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1110,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>08:23</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,10 +1137,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123675730</v>
+        <v>123675773</v>
       </c>
       <c r="B6" t="n">
-        <v>78788</v>
+        <v>79898</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,25 +1149,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1177,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>540340</v>
+        <v>540495</v>
       </c>
       <c r="R6" t="n">
-        <v>7200020</v>
+        <v>7199932</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1198,7 +1212,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>08:03</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1222,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>08:03</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,7 +1249,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123675732</v>
+        <v>123675766</v>
       </c>
       <c r="B7" t="n">
         <v>78788</v>
@@ -1275,10 +1289,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>540171</v>
+        <v>540428</v>
       </c>
       <c r="R7" t="n">
-        <v>7200163</v>
+        <v>7199871</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1310,7 +1324,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>08:23</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1320,7 +1334,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>08:23</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,10 +1361,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123675764</v>
+        <v>123675719</v>
       </c>
       <c r="B8" t="n">
-        <v>78867</v>
+        <v>78788</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1363,21 +1377,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1387,10 +1401,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>540428</v>
+        <v>540622</v>
       </c>
       <c r="R8" t="n">
-        <v>7199871</v>
+        <v>7199937</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1422,7 +1436,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>08:23</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1432,7 +1446,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>08:23</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1459,10 +1473,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123675724</v>
+        <v>123675775</v>
       </c>
       <c r="B9" t="n">
-        <v>79905</v>
+        <v>82575</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1471,25 +1485,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6464</v>
+        <v>1312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1499,10 +1513,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>540524</v>
+        <v>540545</v>
       </c>
       <c r="R9" t="n">
-        <v>7199906</v>
+        <v>7199990</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1534,7 +1548,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>07:55</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1544,7 +1558,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>07:55</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1571,10 +1585,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123675728</v>
+        <v>123675753</v>
       </c>
       <c r="B10" t="n">
-        <v>56700</v>
+        <v>78788</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1583,43 +1597,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>540526</v>
+        <v>540320</v>
       </c>
       <c r="R10" t="n">
-        <v>7199833</v>
+        <v>7199929</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1651,7 +1660,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1661,7 +1670,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1688,10 +1697,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123675761</v>
+        <v>123675755</v>
       </c>
       <c r="B11" t="n">
-        <v>78788</v>
+        <v>57644</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1704,34 +1713,43 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>540369</v>
+        <v>540398</v>
       </c>
       <c r="R11" t="n">
-        <v>7199910</v>
+        <v>7199894</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1763,7 +1781,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>08:37</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1773,7 +1791,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>08:37</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1800,7 +1818,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123675719</v>
+        <v>123675783</v>
       </c>
       <c r="B12" t="n">
         <v>78788</v>
@@ -1840,10 +1858,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>540622</v>
+        <v>540760</v>
       </c>
       <c r="R12" t="n">
-        <v>7199937</v>
+        <v>7200064</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1875,7 +1893,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1885,7 +1903,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1912,10 +1930,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123675726</v>
+        <v>123675728</v>
       </c>
       <c r="B13" t="n">
-        <v>79898</v>
+        <v>56700</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1928,34 +1946,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6462</v>
+        <v>100138</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>540524</v>
+        <v>540526</v>
       </c>
       <c r="R13" t="n">
-        <v>7199907</v>
+        <v>7199833</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1987,7 +2010,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1997,7 +2020,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2136,10 +2159,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123675767</v>
+        <v>123675756</v>
       </c>
       <c r="B15" t="n">
-        <v>78874</v>
+        <v>57644</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2148,38 +2171,47 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6450</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>540427</v>
+        <v>540336</v>
       </c>
       <c r="R15" t="n">
-        <v>7199883</v>
+        <v>7199942</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2211,7 +2243,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2221,7 +2253,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2365,7 +2397,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123675771</v>
+        <v>123675779</v>
       </c>
       <c r="B17" t="n">
         <v>57491</v>
@@ -2398,10 +2430,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2410,13 +2446,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>540488</v>
+        <v>540603</v>
       </c>
       <c r="R17" t="n">
-        <v>7199896</v>
+        <v>7199887</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2445,7 +2481,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:32</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2455,7 +2491,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:32</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2482,10 +2518,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123675779</v>
+        <v>123675736</v>
       </c>
       <c r="B18" t="n">
-        <v>57491</v>
+        <v>78788</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2498,46 +2534,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>540603</v>
+        <v>540078</v>
       </c>
       <c r="R18" t="n">
-        <v>7199887</v>
+        <v>7199948</v>
       </c>
       <c r="S18" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2566,7 +2593,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>07:32</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2576,7 +2603,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>07:32</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2603,10 +2630,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123675722</v>
+        <v>123675735</v>
       </c>
       <c r="B19" t="n">
-        <v>79829</v>
+        <v>57491</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2615,38 +2642,43 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>229497</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>540541</v>
+        <v>540080</v>
       </c>
       <c r="R19" t="n">
-        <v>7199839</v>
+        <v>7199959</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2678,7 +2710,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2688,7 +2720,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2715,10 +2747,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123675753</v>
+        <v>123675771</v>
       </c>
       <c r="B20" t="n">
-        <v>78788</v>
+        <v>57491</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2731,34 +2763,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>540320</v>
+        <v>540488</v>
       </c>
       <c r="R20" t="n">
-        <v>7199929</v>
+        <v>7199896</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2790,7 +2827,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2800,7 +2837,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2827,10 +2864,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123675773</v>
+        <v>123675752</v>
       </c>
       <c r="B21" t="n">
-        <v>79898</v>
+        <v>57491</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2839,38 +2876,43 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>540495</v>
+        <v>540320</v>
       </c>
       <c r="R21" t="n">
-        <v>7199932</v>
+        <v>7199929</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2902,7 +2944,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>08:03</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2912,7 +2954,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>08:03</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2939,10 +2981,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123675750</v>
+        <v>123675720</v>
       </c>
       <c r="B22" t="n">
-        <v>78788</v>
+        <v>57491</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2955,34 +2997,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>540220</v>
+        <v>540612</v>
       </c>
       <c r="R22" t="n">
-        <v>7199934</v>
+        <v>7199895</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3014,7 +3061,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>08:57</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3024,7 +3071,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>08:57</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3051,7 +3098,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123675736</v>
+        <v>123675730</v>
       </c>
       <c r="B23" t="n">
         <v>78788</v>
@@ -3091,10 +3138,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>540078</v>
+        <v>540340</v>
       </c>
       <c r="R23" t="n">
-        <v>7199948</v>
+        <v>7200020</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3126,7 +3173,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3136,7 +3183,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3163,10 +3210,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123675725</v>
+        <v>123675778</v>
       </c>
       <c r="B24" t="n">
-        <v>78788</v>
+        <v>74879</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3179,21 +3226,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3203,10 +3250,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>540523</v>
+        <v>540666</v>
       </c>
       <c r="R24" t="n">
-        <v>7199906</v>
+        <v>7200065</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3238,7 +3285,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>07:38</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3248,7 +3295,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>07:38</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3275,10 +3322,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123675735</v>
+        <v>123675757</v>
       </c>
       <c r="B25" t="n">
-        <v>57491</v>
+        <v>57644</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3291,27 +3338,31 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3320,10 +3371,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>540080</v>
+        <v>540316</v>
       </c>
       <c r="R25" t="n">
-        <v>7199959</v>
+        <v>7200001</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3355,7 +3406,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3365,7 +3416,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3392,10 +3443,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123675718</v>
+        <v>123675763</v>
       </c>
       <c r="B26" t="n">
-        <v>56700</v>
+        <v>77731</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3404,43 +3455,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100138</v>
+        <v>314</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>540623</v>
+        <v>540425</v>
       </c>
       <c r="R26" t="n">
-        <v>7199942</v>
+        <v>7199890</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3472,7 +3518,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>08:27</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3482,7 +3528,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>08:27</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3509,10 +3555,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123675755</v>
+        <v>123675726</v>
       </c>
       <c r="B27" t="n">
-        <v>57644</v>
+        <v>79898</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3521,47 +3567,38 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103021</v>
+        <v>6462</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>540398</v>
+        <v>540524</v>
       </c>
       <c r="R27" t="n">
-        <v>7199894</v>
+        <v>7199907</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3593,7 +3630,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3603,7 +3640,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3630,10 +3667,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123675749</v>
+        <v>123675770</v>
       </c>
       <c r="B28" t="n">
-        <v>57507</v>
+        <v>78788</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3646,39 +3683,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>540220</v>
+        <v>540474</v>
       </c>
       <c r="R28" t="n">
-        <v>7199936</v>
+        <v>7199895</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3710,7 +3742,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>08:57</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3720,7 +3752,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>08:57</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3747,10 +3779,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123675752</v>
+        <v>123675732</v>
       </c>
       <c r="B29" t="n">
-        <v>57491</v>
+        <v>78788</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3763,39 +3795,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>540320</v>
+        <v>540171</v>
       </c>
       <c r="R29" t="n">
-        <v>7199929</v>
+        <v>7200163</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3827,7 +3854,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3837,7 +3864,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3985,10 +4012,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123675775</v>
+        <v>123675737</v>
       </c>
       <c r="B31" t="n">
-        <v>82575</v>
+        <v>78788</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4001,21 +4028,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4025,10 +4052,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>540545</v>
+        <v>540120</v>
       </c>
       <c r="R31" t="n">
-        <v>7199990</v>
+        <v>7199910</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4060,7 +4087,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>07:55</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4070,7 +4097,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>07:55</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4097,10 +4124,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123675757</v>
+        <v>123675724</v>
       </c>
       <c r="B32" t="n">
-        <v>57644</v>
+        <v>79905</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4109,47 +4136,38 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>103021</v>
+        <v>6464</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>540316</v>
+        <v>540524</v>
       </c>
       <c r="R32" t="n">
-        <v>7200001</v>
+        <v>7199906</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4181,7 +4199,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4191,7 +4209,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4218,10 +4236,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123675763</v>
+        <v>123675749</v>
       </c>
       <c r="B33" t="n">
-        <v>77731</v>
+        <v>57507</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4234,34 +4252,39 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>314</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>540425</v>
+        <v>540220</v>
       </c>
       <c r="R33" t="n">
-        <v>7199890</v>
+        <v>7199936</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4293,7 +4316,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>08:27</t>
+          <t>08:57</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4303,7 +4326,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>08:27</t>
+          <t>08:57</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4330,10 +4353,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123675783</v>
+        <v>123675718</v>
       </c>
       <c r="B34" t="n">
-        <v>78788</v>
+        <v>56700</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4342,38 +4365,43 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>540760</v>
+        <v>540623</v>
       </c>
       <c r="R34" t="n">
-        <v>7200064</v>
+        <v>7199942</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4405,7 +4433,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4415,7 +4443,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4442,10 +4470,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123675751</v>
+        <v>123675738</v>
       </c>
       <c r="B35" t="n">
-        <v>78788</v>
+        <v>78867</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4458,21 +4486,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4482,10 +4510,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>540269</v>
+        <v>540142</v>
       </c>
       <c r="R35" t="n">
-        <v>7199949</v>
+        <v>7199918</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4517,7 +4545,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>08:54</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4527,7 +4555,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>08:54</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4554,10 +4582,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123675759</v>
+        <v>123675723</v>
       </c>
       <c r="B36" t="n">
-        <v>57861</v>
+        <v>79898</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4570,43 +4598,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>103015</v>
+        <v>6462</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>540345</v>
+        <v>540541</v>
       </c>
       <c r="R36" t="n">
-        <v>7199934</v>
+        <v>7199839</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4638,7 +4657,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4648,7 +4667,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4675,10 +4694,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123675762</v>
+        <v>123675774</v>
       </c>
       <c r="B37" t="n">
-        <v>57507</v>
+        <v>78788</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4691,39 +4710,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>540423</v>
+        <v>540546</v>
       </c>
       <c r="R37" t="n">
-        <v>7199851</v>
+        <v>7199996</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4755,7 +4769,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>07:56</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4765,7 +4779,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>07:56</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4792,10 +4806,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123675720</v>
+        <v>123675722</v>
       </c>
       <c r="B38" t="n">
-        <v>57491</v>
+        <v>79829</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4804,43 +4818,38 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>229497</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>540612</v>
+        <v>540541</v>
       </c>
       <c r="R38" t="n">
-        <v>7199895</v>
+        <v>7199839</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4872,7 +4881,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4882,7 +4891,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4909,10 +4918,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123675781</v>
+        <v>123675767</v>
       </c>
       <c r="B39" t="n">
-        <v>57861</v>
+        <v>78874</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4925,43 +4934,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>103015</v>
+        <v>6450</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Ach.) Parrique</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>540728</v>
+        <v>540427</v>
       </c>
       <c r="R39" t="n">
-        <v>7200067</v>
+        <v>7199883</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4993,7 +4993,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>07:29</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5003,7 +5003,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>07:29</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5030,10 +5030,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123675723</v>
+        <v>123675781</v>
       </c>
       <c r="B40" t="n">
-        <v>79898</v>
+        <v>57861</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5046,34 +5046,43 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6462</v>
+        <v>103015</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>540541</v>
+        <v>540728</v>
       </c>
       <c r="R40" t="n">
-        <v>7199839</v>
+        <v>7200067</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -5105,7 +5114,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>07:29</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5115,7 +5124,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>07:29</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5142,10 +5151,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123675739</v>
+        <v>123675754</v>
       </c>
       <c r="B41" t="n">
-        <v>78788</v>
+        <v>91008</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5158,21 +5167,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5182,10 +5191,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>540140</v>
+        <v>540318</v>
       </c>
       <c r="R41" t="n">
-        <v>7199918</v>
+        <v>7199932</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5217,7 +5226,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5227,7 +5236,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5254,7 +5263,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123675768</v>
+        <v>123675750</v>
       </c>
       <c r="B42" t="n">
         <v>78788</v>
@@ -5294,10 +5303,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>540469</v>
+        <v>540220</v>
       </c>
       <c r="R42" t="n">
-        <v>7199898</v>
+        <v>7199934</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5329,7 +5338,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>08:57</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5339,7 +5348,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>08:57</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5366,7 +5375,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123675774</v>
+        <v>123675768</v>
       </c>
       <c r="B43" t="n">
         <v>78788</v>
@@ -5406,10 +5415,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>540546</v>
+        <v>540469</v>
       </c>
       <c r="R43" t="n">
-        <v>7199996</v>
+        <v>7199898</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5441,7 +5450,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>07:56</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5451,7 +5460,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>07:56</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5478,7 +5487,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123675770</v>
+        <v>123675751</v>
       </c>
       <c r="B44" t="n">
         <v>78788</v>
@@ -5518,10 +5527,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>540474</v>
+        <v>540269</v>
       </c>
       <c r="R44" t="n">
-        <v>7199895</v>
+        <v>7199949</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5553,7 +5562,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5563,7 +5572,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5590,10 +5599,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123675737</v>
+        <v>123675764</v>
       </c>
       <c r="B45" t="n">
-        <v>78788</v>
+        <v>78867</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5606,21 +5615,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5630,10 +5639,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>540120</v>
+        <v>540428</v>
       </c>
       <c r="R45" t="n">
-        <v>7199910</v>
+        <v>7199871</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5665,7 +5674,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>08:23</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5675,7 +5684,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>08:23</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5702,7 +5711,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123675772</v>
+        <v>123675761</v>
       </c>
       <c r="B46" t="n">
         <v>78788</v>
@@ -5742,10 +5751,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>540491</v>
+        <v>540369</v>
       </c>
       <c r="R46" t="n">
-        <v>7199896</v>
+        <v>7199910</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5777,7 +5786,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>08:37</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5787,7 +5796,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>08:37</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5814,10 +5823,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123675756</v>
+        <v>123675725</v>
       </c>
       <c r="B47" t="n">
-        <v>57644</v>
+        <v>78788</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5830,43 +5839,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>540336</v>
+        <v>540523</v>
       </c>
       <c r="R47" t="n">
-        <v>7199942</v>
+        <v>7199906</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5898,7 +5898,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5908,7 +5908,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD47" t="b">

--- a/artfynd/A 9827-2025 artfynd.xlsx
+++ b/artfynd/A 9827-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123675762</v>
+        <v>123675738</v>
       </c>
       <c r="B2" t="n">
-        <v>57507</v>
+        <v>78867</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,39 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>864</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>540423</v>
+        <v>540142</v>
       </c>
       <c r="R2" t="n">
-        <v>7199851</v>
+        <v>7199918</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -755,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123675772</v>
+        <v>123675732</v>
       </c>
       <c r="B3" t="n">
         <v>78788</v>
@@ -832,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>540491</v>
+        <v>540171</v>
       </c>
       <c r="R3" t="n">
-        <v>7199896</v>
+        <v>7200163</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -867,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,7 +899,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123675739</v>
+        <v>123675753</v>
       </c>
       <c r="B4" t="n">
         <v>78788</v>
@@ -944,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>540140</v>
+        <v>540320</v>
       </c>
       <c r="R4" t="n">
-        <v>7199918</v>
+        <v>7199929</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -979,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123675759</v>
+        <v>123675737</v>
       </c>
       <c r="B5" t="n">
-        <v>57861</v>
+        <v>78788</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1028,47 +1023,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>540345</v>
+        <v>540120</v>
       </c>
       <c r="R5" t="n">
-        <v>7199934</v>
+        <v>7199910</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1100,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1110,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1137,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123675773</v>
+        <v>123675763</v>
       </c>
       <c r="B6" t="n">
-        <v>79898</v>
+        <v>77731</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1149,25 +1135,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6462</v>
+        <v>314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1177,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>540495</v>
+        <v>540425</v>
       </c>
       <c r="R6" t="n">
-        <v>7199932</v>
+        <v>7199890</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1212,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>08:03</t>
+          <t>08:27</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1222,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>08:03</t>
+          <t>08:27</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1249,7 +1235,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123675766</v>
+        <v>123675768</v>
       </c>
       <c r="B7" t="n">
         <v>78788</v>
@@ -1289,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>540428</v>
+        <v>540469</v>
       </c>
       <c r="R7" t="n">
-        <v>7199871</v>
+        <v>7199898</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1324,7 +1310,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>08:23</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1334,7 +1320,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>08:23</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1361,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123675719</v>
+        <v>123675754</v>
       </c>
       <c r="B8" t="n">
-        <v>78788</v>
+        <v>91008</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1377,21 +1363,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1401,10 +1387,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>540622</v>
+        <v>540318</v>
       </c>
       <c r="R8" t="n">
-        <v>7199937</v>
+        <v>7199932</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1436,7 +1422,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1446,7 +1432,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1473,10 +1459,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123675775</v>
+        <v>123675767</v>
       </c>
       <c r="B9" t="n">
-        <v>82575</v>
+        <v>78874</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1485,25 +1471,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1312</v>
+        <v>6450</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1513,10 +1499,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>540545</v>
+        <v>540427</v>
       </c>
       <c r="R9" t="n">
-        <v>7199990</v>
+        <v>7199883</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1548,7 +1534,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>07:55</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1558,7 +1544,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>07:55</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1585,10 +1571,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123675753</v>
+        <v>123675720</v>
       </c>
       <c r="B10" t="n">
-        <v>78788</v>
+        <v>57491</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1601,34 +1587,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>540320</v>
+        <v>540612</v>
       </c>
       <c r="R10" t="n">
-        <v>7199929</v>
+        <v>7199895</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1660,7 +1651,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1670,7 +1661,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1697,10 +1688,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123675755</v>
+        <v>123675722</v>
       </c>
       <c r="B11" t="n">
-        <v>57644</v>
+        <v>79829</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1709,47 +1700,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>229497</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>540398</v>
+        <v>540541</v>
       </c>
       <c r="R11" t="n">
-        <v>7199894</v>
+        <v>7199839</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1781,7 +1763,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1791,7 +1773,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1818,10 +1800,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123675783</v>
+        <v>123675771</v>
       </c>
       <c r="B12" t="n">
-        <v>78788</v>
+        <v>57491</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1834,34 +1816,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>540760</v>
+        <v>540488</v>
       </c>
       <c r="R12" t="n">
-        <v>7200064</v>
+        <v>7199896</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1893,7 +1880,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1903,7 +1890,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1930,10 +1917,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123675728</v>
+        <v>123675773</v>
       </c>
       <c r="B13" t="n">
-        <v>56700</v>
+        <v>79898</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1946,39 +1933,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100138</v>
+        <v>6462</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>540526</v>
+        <v>540495</v>
       </c>
       <c r="R13" t="n">
-        <v>7199833</v>
+        <v>7199932</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2010,7 +1992,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>08:03</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2020,7 +2002,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>08:03</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2047,10 +2029,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123675769</v>
+        <v>123675781</v>
       </c>
       <c r="B14" t="n">
-        <v>96957</v>
+        <v>57861</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2063,34 +2045,43 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221945</v>
+        <v>103015</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>540475</v>
+        <v>540728</v>
       </c>
       <c r="R14" t="n">
-        <v>7199900</v>
+        <v>7200067</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2122,7 +2113,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>07:29</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2132,7 +2123,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>07:29</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2159,10 +2150,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123675756</v>
+        <v>123675730</v>
       </c>
       <c r="B15" t="n">
-        <v>57644</v>
+        <v>78788</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2175,43 +2166,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>540336</v>
+        <v>540340</v>
       </c>
       <c r="R15" t="n">
-        <v>7199942</v>
+        <v>7200020</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2243,7 +2225,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2253,7 +2235,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2280,10 +2262,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123675727</v>
+        <v>123675756</v>
       </c>
       <c r="B16" t="n">
-        <v>56700</v>
+        <v>57644</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2292,31 +2274,35 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2325,10 +2311,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>540500</v>
+        <v>540336</v>
       </c>
       <c r="R16" t="n">
-        <v>7199873</v>
+        <v>7199942</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2360,7 +2346,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2370,7 +2356,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2397,10 +2383,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123675779</v>
+        <v>123675769</v>
       </c>
       <c r="B17" t="n">
-        <v>57491</v>
+        <v>96957</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2409,50 +2395,41 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>540603</v>
+        <v>540475</v>
       </c>
       <c r="R17" t="n">
-        <v>7199887</v>
+        <v>7199900</v>
       </c>
       <c r="S17" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2481,7 +2458,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>07:32</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2491,7 +2468,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>07:32</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2518,10 +2495,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123675736</v>
+        <v>123675749</v>
       </c>
       <c r="B18" t="n">
-        <v>78788</v>
+        <v>57507</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2534,34 +2511,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>540078</v>
+        <v>540220</v>
       </c>
       <c r="R18" t="n">
-        <v>7199948</v>
+        <v>7199936</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2593,7 +2575,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>08:57</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2603,7 +2585,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>08:57</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2630,10 +2612,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123675735</v>
+        <v>123675759</v>
       </c>
       <c r="B19" t="n">
-        <v>57491</v>
+        <v>57861</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2642,20 +2624,20 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>103015</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2663,10 +2645,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2675,10 +2661,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>540080</v>
+        <v>540345</v>
       </c>
       <c r="R19" t="n">
-        <v>7199959</v>
+        <v>7199934</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2710,7 +2696,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2720,7 +2706,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2747,10 +2733,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123675771</v>
+        <v>123675750</v>
       </c>
       <c r="B20" t="n">
-        <v>57491</v>
+        <v>78788</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2763,39 +2749,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>540488</v>
+        <v>540220</v>
       </c>
       <c r="R20" t="n">
-        <v>7199896</v>
+        <v>7199934</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2827,7 +2808,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>08:57</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2837,7 +2818,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>08:57</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2864,10 +2845,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123675752</v>
+        <v>123675783</v>
       </c>
       <c r="B21" t="n">
-        <v>57491</v>
+        <v>78788</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2880,39 +2861,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>540320</v>
+        <v>540760</v>
       </c>
       <c r="R21" t="n">
-        <v>7199929</v>
+        <v>7200064</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2944,7 +2920,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2954,7 +2930,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2981,10 +2957,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123675720</v>
+        <v>123675719</v>
       </c>
       <c r="B22" t="n">
-        <v>57491</v>
+        <v>78788</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2997,39 +2973,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>540612</v>
+        <v>540622</v>
       </c>
       <c r="R22" t="n">
-        <v>7199895</v>
+        <v>7199937</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3061,7 +3032,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3071,7 +3042,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3098,10 +3069,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123675730</v>
+        <v>123675779</v>
       </c>
       <c r="B23" t="n">
-        <v>78788</v>
+        <v>57491</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3114,37 +3085,46 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>540340</v>
+        <v>540603</v>
       </c>
       <c r="R23" t="n">
-        <v>7200020</v>
+        <v>7199887</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3173,7 +3153,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>07:32</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3183,7 +3163,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>07:32</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3210,10 +3190,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123675778</v>
+        <v>123675761</v>
       </c>
       <c r="B24" t="n">
-        <v>74879</v>
+        <v>78788</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3226,21 +3206,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3250,10 +3230,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>540666</v>
+        <v>540369</v>
       </c>
       <c r="R24" t="n">
-        <v>7200065</v>
+        <v>7199910</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3285,7 +3265,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>07:38</t>
+          <t>08:37</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3295,7 +3275,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>07:38</t>
+          <t>08:37</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3322,10 +3302,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123675757</v>
+        <v>123675762</v>
       </c>
       <c r="B25" t="n">
-        <v>57644</v>
+        <v>57507</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3338,31 +3318,27 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3371,10 +3347,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>540316</v>
+        <v>540423</v>
       </c>
       <c r="R25" t="n">
-        <v>7200001</v>
+        <v>7199851</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3406,7 +3382,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3416,7 +3392,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3443,10 +3419,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123675763</v>
+        <v>123675752</v>
       </c>
       <c r="B26" t="n">
-        <v>77731</v>
+        <v>57491</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3459,34 +3435,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>314</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>540425</v>
+        <v>540320</v>
       </c>
       <c r="R26" t="n">
-        <v>7199890</v>
+        <v>7199929</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3518,7 +3499,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>08:27</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3528,7 +3509,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>08:27</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3555,10 +3536,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123675726</v>
+        <v>123675772</v>
       </c>
       <c r="B27" t="n">
-        <v>79898</v>
+        <v>78788</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3567,25 +3548,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3595,10 +3576,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>540524</v>
+        <v>540491</v>
       </c>
       <c r="R27" t="n">
-        <v>7199907</v>
+        <v>7199896</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3630,7 +3611,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3640,7 +3621,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3667,7 +3648,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123675770</v>
+        <v>123675751</v>
       </c>
       <c r="B28" t="n">
         <v>78788</v>
@@ -3707,10 +3688,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>540474</v>
+        <v>540269</v>
       </c>
       <c r="R28" t="n">
-        <v>7199895</v>
+        <v>7199949</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3742,7 +3723,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3752,7 +3733,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3779,10 +3760,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123675732</v>
+        <v>123675735</v>
       </c>
       <c r="B29" t="n">
-        <v>78788</v>
+        <v>57491</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3795,34 +3776,39 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>540171</v>
+        <v>540080</v>
       </c>
       <c r="R29" t="n">
-        <v>7200163</v>
+        <v>7199959</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3854,7 +3840,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3864,7 +3850,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4012,10 +3998,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123675737</v>
+        <v>123675727</v>
       </c>
       <c r="B31" t="n">
-        <v>78788</v>
+        <v>56700</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4024,38 +4010,43 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>540120</v>
+        <v>540500</v>
       </c>
       <c r="R31" t="n">
-        <v>7199910</v>
+        <v>7199873</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4087,7 +4078,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4097,7 +4088,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4124,10 +4115,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123675724</v>
+        <v>123675718</v>
       </c>
       <c r="B32" t="n">
-        <v>79905</v>
+        <v>56700</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4140,34 +4131,39 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6464</v>
+        <v>100138</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>540524</v>
+        <v>540623</v>
       </c>
       <c r="R32" t="n">
-        <v>7199906</v>
+        <v>7199942</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4199,7 +4195,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4209,7 +4205,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4236,10 +4232,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123675749</v>
+        <v>123675739</v>
       </c>
       <c r="B33" t="n">
-        <v>57507</v>
+        <v>78788</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4252,39 +4248,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>540220</v>
+        <v>540140</v>
       </c>
       <c r="R33" t="n">
-        <v>7199936</v>
+        <v>7199918</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4316,7 +4307,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>08:57</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4326,7 +4317,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>08:57</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4353,10 +4344,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123675718</v>
+        <v>123675736</v>
       </c>
       <c r="B34" t="n">
-        <v>56700</v>
+        <v>78788</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4365,43 +4356,38 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>540623</v>
+        <v>540078</v>
       </c>
       <c r="R34" t="n">
-        <v>7199942</v>
+        <v>7199948</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4433,7 +4419,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4443,7 +4429,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4470,10 +4456,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123675738</v>
+        <v>123675728</v>
       </c>
       <c r="B35" t="n">
-        <v>78867</v>
+        <v>56700</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4482,38 +4468,43 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>864</v>
+        <v>100138</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>540142</v>
+        <v>540526</v>
       </c>
       <c r="R35" t="n">
-        <v>7199918</v>
+        <v>7199833</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4545,7 +4536,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4555,7 +4546,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4582,10 +4573,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123675723</v>
+        <v>123675724</v>
       </c>
       <c r="B36" t="n">
-        <v>79898</v>
+        <v>79905</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4598,21 +4589,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6462</v>
+        <v>6464</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4622,10 +4613,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>540541</v>
+        <v>540524</v>
       </c>
       <c r="R36" t="n">
-        <v>7199839</v>
+        <v>7199906</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4657,7 +4648,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4667,7 +4658,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4694,10 +4685,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123675774</v>
+        <v>123675723</v>
       </c>
       <c r="B37" t="n">
-        <v>78788</v>
+        <v>79898</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4706,25 +4697,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4734,10 +4725,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>540546</v>
+        <v>540541</v>
       </c>
       <c r="R37" t="n">
-        <v>7199996</v>
+        <v>7199839</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4769,7 +4760,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>07:56</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4779,7 +4770,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>07:56</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4806,10 +4797,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123675722</v>
+        <v>123675778</v>
       </c>
       <c r="B38" t="n">
-        <v>79829</v>
+        <v>74879</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4818,25 +4809,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>229497</v>
+        <v>6440</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4846,10 +4837,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>540541</v>
+        <v>540666</v>
       </c>
       <c r="R38" t="n">
-        <v>7199839</v>
+        <v>7200065</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4881,7 +4872,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>07:38</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4891,7 +4882,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>07:38</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4918,10 +4909,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123675767</v>
+        <v>123675755</v>
       </c>
       <c r="B39" t="n">
-        <v>78874</v>
+        <v>57644</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4930,38 +4921,47 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6450</v>
+        <v>103021</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>540427</v>
+        <v>540398</v>
       </c>
       <c r="R39" t="n">
-        <v>7199883</v>
+        <v>7199894</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4993,7 +4993,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5003,7 +5003,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5030,10 +5030,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123675781</v>
+        <v>123675764</v>
       </c>
       <c r="B40" t="n">
-        <v>57861</v>
+        <v>78867</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5042,47 +5042,38 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>103015</v>
+        <v>864</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Lynge) Ahti</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>540728</v>
+        <v>540428</v>
       </c>
       <c r="R40" t="n">
-        <v>7200067</v>
+        <v>7199871</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -5114,7 +5105,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>07:29</t>
+          <t>08:23</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5124,7 +5115,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>07:29</t>
+          <t>08:23</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5151,10 +5142,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123675754</v>
+        <v>123675775</v>
       </c>
       <c r="B41" t="n">
-        <v>91008</v>
+        <v>82575</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5167,21 +5158,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5191,10 +5182,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>540318</v>
+        <v>540545</v>
       </c>
       <c r="R41" t="n">
-        <v>7199932</v>
+        <v>7199990</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5226,7 +5217,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>07:55</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5236,7 +5227,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>07:55</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5263,7 +5254,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123675750</v>
+        <v>123675766</v>
       </c>
       <c r="B42" t="n">
         <v>78788</v>
@@ -5303,10 +5294,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>540220</v>
+        <v>540428</v>
       </c>
       <c r="R42" t="n">
-        <v>7199934</v>
+        <v>7199871</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5338,7 +5329,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>08:57</t>
+          <t>08:23</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5348,7 +5339,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>08:57</t>
+          <t>08:23</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5375,7 +5366,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123675768</v>
+        <v>123675770</v>
       </c>
       <c r="B43" t="n">
         <v>78788</v>
@@ -5415,10 +5406,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>540469</v>
+        <v>540474</v>
       </c>
       <c r="R43" t="n">
-        <v>7199898</v>
+        <v>7199895</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5450,7 +5441,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5460,7 +5451,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5487,10 +5478,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123675751</v>
+        <v>123675757</v>
       </c>
       <c r="B44" t="n">
-        <v>78788</v>
+        <v>57644</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5503,34 +5494,43 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>540269</v>
+        <v>540316</v>
       </c>
       <c r="R44" t="n">
-        <v>7199949</v>
+        <v>7200001</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5562,7 +5562,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>08:54</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5572,7 +5572,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>08:54</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5599,10 +5599,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123675764</v>
+        <v>123675725</v>
       </c>
       <c r="B45" t="n">
-        <v>78867</v>
+        <v>78788</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5615,21 +5615,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5639,10 +5639,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>540428</v>
+        <v>540523</v>
       </c>
       <c r="R45" t="n">
-        <v>7199871</v>
+        <v>7199906</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5674,7 +5674,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>08:23</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5684,7 +5684,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>08:23</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5711,10 +5711,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123675761</v>
+        <v>123675726</v>
       </c>
       <c r="B46" t="n">
-        <v>78788</v>
+        <v>79898</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5723,25 +5723,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5751,10 +5751,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>540369</v>
+        <v>540524</v>
       </c>
       <c r="R46" t="n">
-        <v>7199910</v>
+        <v>7199907</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5786,7 +5786,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>08:37</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5796,7 +5796,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>08:37</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5823,7 +5823,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123675725</v>
+        <v>123675774</v>
       </c>
       <c r="B47" t="n">
         <v>78788</v>
@@ -5863,10 +5863,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>540523</v>
+        <v>540546</v>
       </c>
       <c r="R47" t="n">
-        <v>7199906</v>
+        <v>7199996</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5898,7 +5898,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>07:56</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5908,7 +5908,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>07:56</t>
         </is>
       </c>
       <c r="AD47" t="b">

--- a/artfynd/A 9827-2025 artfynd.xlsx
+++ b/artfynd/A 9827-2025 artfynd.xlsx
@@ -1688,10 +1688,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123675722</v>
+        <v>123675771</v>
       </c>
       <c r="B11" t="n">
-        <v>79829</v>
+        <v>57491</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1700,38 +1700,43 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>229497</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>540541</v>
+        <v>540488</v>
       </c>
       <c r="R11" t="n">
-        <v>7199839</v>
+        <v>7199896</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1763,7 +1768,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1773,7 +1778,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1800,10 +1805,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123675771</v>
+        <v>123675722</v>
       </c>
       <c r="B12" t="n">
-        <v>57491</v>
+        <v>79829</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1812,43 +1817,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>229497</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>540488</v>
+        <v>540541</v>
       </c>
       <c r="R12" t="n">
-        <v>7199896</v>
+        <v>7199839</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1880,7 +1880,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2495,10 +2495,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123675749</v>
+        <v>123675759</v>
       </c>
       <c r="B18" t="n">
-        <v>57507</v>
+        <v>57861</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2507,20 +2507,20 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2528,10 +2528,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2540,10 +2544,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>540220</v>
+        <v>540345</v>
       </c>
       <c r="R18" t="n">
-        <v>7199936</v>
+        <v>7199934</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2575,7 +2579,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>08:57</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2585,7 +2589,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>08:57</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2612,10 +2616,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123675759</v>
+        <v>123675749</v>
       </c>
       <c r="B19" t="n">
-        <v>57861</v>
+        <v>57507</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2624,20 +2628,20 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2645,14 +2649,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>540345</v>
+        <v>540220</v>
       </c>
       <c r="R19" t="n">
-        <v>7199934</v>
+        <v>7199936</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2696,7 +2696,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>08:57</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2706,7 +2706,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>08:57</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3302,10 +3302,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123675762</v>
+        <v>123675752</v>
       </c>
       <c r="B25" t="n">
-        <v>57507</v>
+        <v>57491</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3318,16 +3318,16 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3347,10 +3347,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>540423</v>
+        <v>540320</v>
       </c>
       <c r="R25" t="n">
-        <v>7199851</v>
+        <v>7199929</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3382,7 +3382,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3392,7 +3392,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3419,10 +3419,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123675752</v>
+        <v>123675762</v>
       </c>
       <c r="B26" t="n">
-        <v>57491</v>
+        <v>57507</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3435,16 +3435,16 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3464,10 +3464,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>540320</v>
+        <v>540423</v>
       </c>
       <c r="R26" t="n">
-        <v>7199929</v>
+        <v>7199851</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3499,7 +3499,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3509,7 +3509,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3760,10 +3760,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123675735</v>
+        <v>123675727</v>
       </c>
       <c r="B29" t="n">
-        <v>57491</v>
+        <v>56700</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3772,31 +3772,31 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3805,10 +3805,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>540080</v>
+        <v>540500</v>
       </c>
       <c r="R29" t="n">
-        <v>7199959</v>
+        <v>7199873</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3840,7 +3840,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3850,7 +3850,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3877,10 +3877,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123675780</v>
+        <v>123675718</v>
       </c>
       <c r="B30" t="n">
-        <v>58169</v>
+        <v>56700</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3893,31 +3893,27 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>103044</v>
+        <v>100138</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3926,10 +3922,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>540723</v>
+        <v>540623</v>
       </c>
       <c r="R30" t="n">
-        <v>7200075</v>
+        <v>7199942</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3961,7 +3957,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>07:29</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3971,7 +3967,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>07:29</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3998,10 +3994,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123675727</v>
+        <v>123675780</v>
       </c>
       <c r="B31" t="n">
-        <v>56700</v>
+        <v>58169</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4014,27 +4010,31 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100138</v>
+        <v>103044</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -4043,10 +4043,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>540500</v>
+        <v>540723</v>
       </c>
       <c r="R31" t="n">
-        <v>7199873</v>
+        <v>7200075</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4078,7 +4078,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>07:29</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4088,7 +4088,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>07:29</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4115,10 +4115,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123675718</v>
+        <v>123675739</v>
       </c>
       <c r="B32" t="n">
-        <v>56700</v>
+        <v>78788</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4127,43 +4127,38 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>540623</v>
+        <v>540140</v>
       </c>
       <c r="R32" t="n">
-        <v>7199942</v>
+        <v>7199918</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4195,7 +4190,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4205,7 +4200,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4232,7 +4227,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123675739</v>
+        <v>123675736</v>
       </c>
       <c r="B33" t="n">
         <v>78788</v>
@@ -4272,10 +4267,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>540140</v>
+        <v>540078</v>
       </c>
       <c r="R33" t="n">
-        <v>7199918</v>
+        <v>7199948</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4307,7 +4302,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4317,7 +4312,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4344,10 +4339,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123675736</v>
+        <v>123675735</v>
       </c>
       <c r="B34" t="n">
-        <v>78788</v>
+        <v>57491</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4360,34 +4355,39 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>540078</v>
+        <v>540080</v>
       </c>
       <c r="R34" t="n">
-        <v>7199948</v>
+        <v>7199959</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4573,10 +4573,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123675724</v>
+        <v>123675723</v>
       </c>
       <c r="B36" t="n">
-        <v>79905</v>
+        <v>79898</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4589,21 +4589,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4613,10 +4613,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>540524</v>
+        <v>540541</v>
       </c>
       <c r="R36" t="n">
-        <v>7199906</v>
+        <v>7199839</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4648,7 +4648,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4658,7 +4658,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4685,10 +4685,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123675723</v>
+        <v>123675724</v>
       </c>
       <c r="B37" t="n">
-        <v>79898</v>
+        <v>79905</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4701,21 +4701,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6462</v>
+        <v>6464</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4725,10 +4725,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>540541</v>
+        <v>540524</v>
       </c>
       <c r="R37" t="n">
-        <v>7199839</v>
+        <v>7199906</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4760,7 +4760,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4770,7 +4770,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4909,10 +4909,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123675755</v>
+        <v>123675764</v>
       </c>
       <c r="B39" t="n">
-        <v>57644</v>
+        <v>78867</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4925,43 +4925,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>103021</v>
+        <v>864</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Lynge) Ahti</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>540398</v>
+        <v>540428</v>
       </c>
       <c r="R39" t="n">
-        <v>7199894</v>
+        <v>7199871</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4993,7 +4984,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>08:23</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5003,7 +4994,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>08:23</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5030,10 +5021,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123675764</v>
+        <v>123675755</v>
       </c>
       <c r="B40" t="n">
-        <v>78867</v>
+        <v>57644</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5046,34 +5037,43 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>864</v>
+        <v>103021</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>540428</v>
+        <v>540398</v>
       </c>
       <c r="R40" t="n">
-        <v>7199871</v>
+        <v>7199894</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -5105,7 +5105,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>08:23</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5115,7 +5115,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>08:23</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5142,10 +5142,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123675775</v>
+        <v>123675766</v>
       </c>
       <c r="B41" t="n">
-        <v>82575</v>
+        <v>78788</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5158,21 +5158,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5182,10 +5182,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>540545</v>
+        <v>540428</v>
       </c>
       <c r="R41" t="n">
-        <v>7199990</v>
+        <v>7199871</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5217,7 +5217,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>07:55</t>
+          <t>08:23</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5227,7 +5227,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>07:55</t>
+          <t>08:23</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5254,7 +5254,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123675766</v>
+        <v>123675770</v>
       </c>
       <c r="B42" t="n">
         <v>78788</v>
@@ -5294,10 +5294,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>540428</v>
+        <v>540474</v>
       </c>
       <c r="R42" t="n">
-        <v>7199871</v>
+        <v>7199895</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5329,7 +5329,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>08:23</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5339,7 +5339,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>08:23</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5366,10 +5366,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123675770</v>
+        <v>123675775</v>
       </c>
       <c r="B43" t="n">
-        <v>78788</v>
+        <v>82575</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5382,21 +5382,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5406,10 +5406,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>540474</v>
+        <v>540545</v>
       </c>
       <c r="R43" t="n">
-        <v>7199895</v>
+        <v>7199990</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5441,7 +5441,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>07:55</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5451,7 +5451,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>07:55</t>
         </is>
       </c>
       <c r="AD43" t="b">

--- a/artfynd/A 9827-2025 artfynd.xlsx
+++ b/artfynd/A 9827-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123675738</v>
+        <v>123675732</v>
       </c>
       <c r="B2" t="n">
-        <v>78867</v>
+        <v>78788</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>540142</v>
+        <v>540171</v>
       </c>
       <c r="R2" t="n">
-        <v>7199918</v>
+        <v>7200163</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123675732</v>
+        <v>123675722</v>
       </c>
       <c r="B3" t="n">
-        <v>78788</v>
+        <v>79829</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,25 +799,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>540171</v>
+        <v>540541</v>
       </c>
       <c r="R3" t="n">
-        <v>7200163</v>
+        <v>7199839</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123675753</v>
+        <v>123675775</v>
       </c>
       <c r="B4" t="n">
-        <v>78788</v>
+        <v>82575</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,21 +915,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>540320</v>
+        <v>540545</v>
       </c>
       <c r="R4" t="n">
-        <v>7199929</v>
+        <v>7199990</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>07:55</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>07:55</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123675737</v>
+        <v>123675728</v>
       </c>
       <c r="B5" t="n">
-        <v>78788</v>
+        <v>56700</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,38 +1023,43 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>540120</v>
+        <v>540526</v>
       </c>
       <c r="R5" t="n">
-        <v>7199910</v>
+        <v>7199833</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1086,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1101,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,10 +1128,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123675763</v>
+        <v>123675769</v>
       </c>
       <c r="B6" t="n">
-        <v>77731</v>
+        <v>96957</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,25 +1140,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>314</v>
+        <v>221945</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1168,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>540425</v>
+        <v>540475</v>
       </c>
       <c r="R6" t="n">
-        <v>7199890</v>
+        <v>7199900</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1198,7 +1203,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>08:27</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1213,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>08:27</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,10 +1240,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123675768</v>
+        <v>123675723</v>
       </c>
       <c r="B7" t="n">
-        <v>78788</v>
+        <v>79898</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1247,25 +1252,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1280,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>540469</v>
+        <v>540541</v>
       </c>
       <c r="R7" t="n">
-        <v>7199898</v>
+        <v>7199839</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1310,7 +1315,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1320,7 +1325,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,10 +1352,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123675754</v>
+        <v>123675766</v>
       </c>
       <c r="B8" t="n">
-        <v>91008</v>
+        <v>78788</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1363,21 +1368,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1387,10 +1392,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>540318</v>
+        <v>540428</v>
       </c>
       <c r="R8" t="n">
-        <v>7199932</v>
+        <v>7199871</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1422,7 +1427,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>08:23</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1432,7 +1437,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>08:23</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1459,10 +1464,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123675767</v>
+        <v>123675727</v>
       </c>
       <c r="B9" t="n">
-        <v>78874</v>
+        <v>56700</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1475,34 +1480,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6450</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>540427</v>
+        <v>540500</v>
       </c>
       <c r="R9" t="n">
-        <v>7199883</v>
+        <v>7199873</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1534,7 +1544,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1544,7 +1554,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1571,10 +1581,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123675720</v>
+        <v>123675757</v>
       </c>
       <c r="B10" t="n">
-        <v>57491</v>
+        <v>57644</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1587,27 +1597,31 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1616,10 +1630,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>540612</v>
+        <v>540316</v>
       </c>
       <c r="R10" t="n">
-        <v>7199895</v>
+        <v>7200001</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1651,7 +1665,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1661,7 +1675,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1688,10 +1702,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123675771</v>
+        <v>123675756</v>
       </c>
       <c r="B11" t="n">
-        <v>57491</v>
+        <v>57644</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1704,27 +1718,31 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1733,10 +1751,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>540488</v>
+        <v>540336</v>
       </c>
       <c r="R11" t="n">
-        <v>7199896</v>
+        <v>7199942</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1768,7 +1786,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1778,7 +1796,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1805,10 +1823,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123675722</v>
+        <v>123675768</v>
       </c>
       <c r="B12" t="n">
-        <v>79829</v>
+        <v>78788</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1817,25 +1835,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1845,10 +1863,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>540541</v>
+        <v>540469</v>
       </c>
       <c r="R12" t="n">
-        <v>7199839</v>
+        <v>7199898</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1880,7 +1898,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1890,7 +1908,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1917,10 +1935,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123675773</v>
+        <v>123675718</v>
       </c>
       <c r="B13" t="n">
-        <v>79898</v>
+        <v>56700</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1933,34 +1951,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6462</v>
+        <v>100138</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>540495</v>
+        <v>540623</v>
       </c>
       <c r="R13" t="n">
-        <v>7199932</v>
+        <v>7199942</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1992,7 +2015,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>08:03</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2002,7 +2025,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>08:03</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2029,10 +2052,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123675781</v>
+        <v>123675779</v>
       </c>
       <c r="B14" t="n">
-        <v>57861</v>
+        <v>57491</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2041,20 +2064,20 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103015</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2069,7 +2092,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2078,13 +2101,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>540728</v>
+        <v>540603</v>
       </c>
       <c r="R14" t="n">
-        <v>7200067</v>
+        <v>7199887</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2113,7 +2136,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>07:29</t>
+          <t>07:32</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2123,7 +2146,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>07:29</t>
+          <t>07:32</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2150,10 +2173,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123675730</v>
+        <v>123675781</v>
       </c>
       <c r="B15" t="n">
-        <v>78788</v>
+        <v>57861</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2162,38 +2185,47 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>540340</v>
+        <v>540728</v>
       </c>
       <c r="R15" t="n">
-        <v>7200020</v>
+        <v>7200067</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2225,7 +2257,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>07:29</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2235,7 +2267,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>07:29</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2262,10 +2294,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123675756</v>
+        <v>123675780</v>
       </c>
       <c r="B16" t="n">
-        <v>57644</v>
+        <v>58169</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2274,25 +2306,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>103044</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2302,7 +2334,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2311,10 +2343,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>540336</v>
+        <v>540723</v>
       </c>
       <c r="R16" t="n">
-        <v>7199942</v>
+        <v>7200075</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2346,7 +2378,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>07:29</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2356,7 +2388,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>07:29</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2383,10 +2415,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123675769</v>
+        <v>123675737</v>
       </c>
       <c r="B17" t="n">
-        <v>96957</v>
+        <v>78788</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2395,25 +2427,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2423,10 +2455,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>540475</v>
+        <v>540120</v>
       </c>
       <c r="R17" t="n">
-        <v>7199900</v>
+        <v>7199910</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2458,7 +2490,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2468,7 +2500,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2616,10 +2648,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123675749</v>
+        <v>123675764</v>
       </c>
       <c r="B19" t="n">
-        <v>57507</v>
+        <v>78867</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2632,39 +2664,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>864</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>540220</v>
+        <v>540428</v>
       </c>
       <c r="R19" t="n">
-        <v>7199936</v>
+        <v>7199871</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2696,7 +2723,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>08:57</t>
+          <t>08:23</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2706,7 +2733,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>08:57</t>
+          <t>08:23</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2733,7 +2760,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123675750</v>
+        <v>123675774</v>
       </c>
       <c r="B20" t="n">
         <v>78788</v>
@@ -2773,10 +2800,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>540220</v>
+        <v>540546</v>
       </c>
       <c r="R20" t="n">
-        <v>7199934</v>
+        <v>7199996</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2808,7 +2835,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>08:57</t>
+          <t>07:56</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2818,7 +2845,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>08:57</t>
+          <t>07:56</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2845,10 +2872,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123675783</v>
+        <v>123675754</v>
       </c>
       <c r="B21" t="n">
-        <v>78788</v>
+        <v>91008</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2861,21 +2888,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2885,10 +2912,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>540760</v>
+        <v>540318</v>
       </c>
       <c r="R21" t="n">
-        <v>7200064</v>
+        <v>7199932</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2920,7 +2947,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2930,7 +2957,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2957,7 +2984,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123675719</v>
+        <v>123675772</v>
       </c>
       <c r="B22" t="n">
         <v>78788</v>
@@ -2997,10 +3024,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>540622</v>
+        <v>540491</v>
       </c>
       <c r="R22" t="n">
-        <v>7199937</v>
+        <v>7199896</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3032,7 +3059,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3042,7 +3069,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3069,10 +3096,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123675779</v>
+        <v>123675761</v>
       </c>
       <c r="B23" t="n">
-        <v>57491</v>
+        <v>78788</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3085,46 +3112,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>540603</v>
+        <v>540369</v>
       </c>
       <c r="R23" t="n">
-        <v>7199887</v>
+        <v>7199910</v>
       </c>
       <c r="S23" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3153,7 +3171,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>07:32</t>
+          <t>08:37</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3163,7 +3181,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>07:32</t>
+          <t>08:37</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3190,10 +3208,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123675761</v>
+        <v>123675724</v>
       </c>
       <c r="B24" t="n">
-        <v>78788</v>
+        <v>79905</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3202,25 +3220,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3230,10 +3248,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>540369</v>
+        <v>540524</v>
       </c>
       <c r="R24" t="n">
-        <v>7199910</v>
+        <v>7199906</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3265,7 +3283,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>08:37</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3275,7 +3293,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>08:37</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3302,7 +3320,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123675752</v>
+        <v>123675735</v>
       </c>
       <c r="B25" t="n">
         <v>57491</v>
@@ -3338,7 +3356,7 @@
       <c r="I25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3347,10 +3365,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>540320</v>
+        <v>540080</v>
       </c>
       <c r="R25" t="n">
-        <v>7199929</v>
+        <v>7199959</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3382,7 +3400,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3392,7 +3410,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3419,10 +3437,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123675762</v>
+        <v>123675763</v>
       </c>
       <c r="B26" t="n">
-        <v>57507</v>
+        <v>77731</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3435,39 +3453,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>314</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>540423</v>
+        <v>540425</v>
       </c>
       <c r="R26" t="n">
-        <v>7199851</v>
+        <v>7199890</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3499,7 +3512,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>08:27</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3509,7 +3522,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>08:27</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3536,10 +3549,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123675772</v>
+        <v>123675738</v>
       </c>
       <c r="B27" t="n">
-        <v>78788</v>
+        <v>78867</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3552,21 +3565,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3576,10 +3589,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>540491</v>
+        <v>540142</v>
       </c>
       <c r="R27" t="n">
-        <v>7199896</v>
+        <v>7199918</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3611,7 +3624,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3621,7 +3634,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3648,7 +3661,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123675751</v>
+        <v>123675730</v>
       </c>
       <c r="B28" t="n">
         <v>78788</v>
@@ -3688,10 +3701,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>540269</v>
+        <v>540340</v>
       </c>
       <c r="R28" t="n">
-        <v>7199949</v>
+        <v>7200020</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3723,7 +3736,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>08:54</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3733,7 +3746,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>08:54</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3760,10 +3773,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123675727</v>
+        <v>123675736</v>
       </c>
       <c r="B29" t="n">
-        <v>56700</v>
+        <v>78788</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3772,43 +3785,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>540500</v>
+        <v>540078</v>
       </c>
       <c r="R29" t="n">
-        <v>7199873</v>
+        <v>7199948</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3840,7 +3848,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3850,7 +3858,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3877,10 +3885,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123675718</v>
+        <v>123675725</v>
       </c>
       <c r="B30" t="n">
-        <v>56700</v>
+        <v>78788</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3889,43 +3897,38 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>540623</v>
+        <v>540523</v>
       </c>
       <c r="R30" t="n">
-        <v>7199942</v>
+        <v>7199906</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3957,7 +3960,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3967,7 +3970,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3994,10 +3997,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123675780</v>
+        <v>123675771</v>
       </c>
       <c r="B31" t="n">
-        <v>58169</v>
+        <v>57491</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4006,20 +4009,20 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>103044</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -4027,14 +4030,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -4043,10 +4042,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>540723</v>
+        <v>540488</v>
       </c>
       <c r="R31" t="n">
-        <v>7200075</v>
+        <v>7199896</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4078,7 +4077,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>07:29</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4088,7 +4087,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>07:29</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4227,10 +4226,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123675736</v>
+        <v>123675752</v>
       </c>
       <c r="B33" t="n">
-        <v>78788</v>
+        <v>57491</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4243,34 +4242,39 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>540078</v>
+        <v>540320</v>
       </c>
       <c r="R33" t="n">
-        <v>7199948</v>
+        <v>7199929</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4302,7 +4306,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4312,7 +4316,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4339,10 +4343,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123675735</v>
+        <v>123675749</v>
       </c>
       <c r="B34" t="n">
-        <v>57491</v>
+        <v>57507</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4355,16 +4359,16 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -4375,7 +4379,7 @@
       <c r="I34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4384,10 +4388,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>540080</v>
+        <v>540220</v>
       </c>
       <c r="R34" t="n">
-        <v>7199959</v>
+        <v>7199936</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4419,7 +4423,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>08:57</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4429,7 +4433,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>08:57</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4456,10 +4460,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123675728</v>
+        <v>123675719</v>
       </c>
       <c r="B35" t="n">
-        <v>56700</v>
+        <v>78788</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4468,43 +4472,38 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>540526</v>
+        <v>540622</v>
       </c>
       <c r="R35" t="n">
-        <v>7199833</v>
+        <v>7199937</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4536,7 +4535,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4546,7 +4545,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4573,10 +4572,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123675723</v>
+        <v>123675750</v>
       </c>
       <c r="B36" t="n">
-        <v>79898</v>
+        <v>78788</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4585,25 +4584,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4613,10 +4612,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>540541</v>
+        <v>540220</v>
       </c>
       <c r="R36" t="n">
-        <v>7199839</v>
+        <v>7199934</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4648,7 +4647,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>08:57</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4658,7 +4657,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>08:57</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4685,10 +4684,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123675724</v>
+        <v>123675726</v>
       </c>
       <c r="B37" t="n">
-        <v>79905</v>
+        <v>79898</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4701,21 +4700,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4728,7 +4727,7 @@
         <v>540524</v>
       </c>
       <c r="R37" t="n">
-        <v>7199906</v>
+        <v>7199907</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4797,10 +4796,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123675778</v>
+        <v>123675753</v>
       </c>
       <c r="B38" t="n">
-        <v>74879</v>
+        <v>78788</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4813,21 +4812,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4837,10 +4836,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>540666</v>
+        <v>540320</v>
       </c>
       <c r="R38" t="n">
-        <v>7200065</v>
+        <v>7199929</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4872,7 +4871,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>07:38</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4882,7 +4881,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>07:38</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4909,10 +4908,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123675764</v>
+        <v>123675751</v>
       </c>
       <c r="B39" t="n">
-        <v>78867</v>
+        <v>78788</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4925,21 +4924,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4949,10 +4948,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>540428</v>
+        <v>540269</v>
       </c>
       <c r="R39" t="n">
-        <v>7199871</v>
+        <v>7199949</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4984,7 +4983,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>08:23</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4994,7 +4993,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>08:23</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5021,10 +5020,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123675755</v>
+        <v>123675767</v>
       </c>
       <c r="B40" t="n">
-        <v>57644</v>
+        <v>78874</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5033,47 +5032,38 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>103021</v>
+        <v>6450</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Ach.) Parrique</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>540398</v>
+        <v>540427</v>
       </c>
       <c r="R40" t="n">
-        <v>7199894</v>
+        <v>7199883</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -5105,7 +5095,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5115,7 +5105,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5142,7 +5132,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123675766</v>
+        <v>123675770</v>
       </c>
       <c r="B41" t="n">
         <v>78788</v>
@@ -5182,10 +5172,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>540428</v>
+        <v>540474</v>
       </c>
       <c r="R41" t="n">
-        <v>7199871</v>
+        <v>7199895</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5217,7 +5207,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>08:23</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5227,7 +5217,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>08:23</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5254,7 +5244,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123675770</v>
+        <v>123675783</v>
       </c>
       <c r="B42" t="n">
         <v>78788</v>
@@ -5294,10 +5284,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>540474</v>
+        <v>540760</v>
       </c>
       <c r="R42" t="n">
-        <v>7199895</v>
+        <v>7200064</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5329,7 +5319,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5339,7 +5329,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5366,10 +5356,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123675775</v>
+        <v>123675755</v>
       </c>
       <c r="B43" t="n">
-        <v>82575</v>
+        <v>57644</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5382,34 +5372,43 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1312</v>
+        <v>103021</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>540545</v>
+        <v>540398</v>
       </c>
       <c r="R43" t="n">
-        <v>7199990</v>
+        <v>7199894</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5441,7 +5440,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>07:55</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5451,7 +5450,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>07:55</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5478,10 +5477,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123675757</v>
+        <v>123675773</v>
       </c>
       <c r="B44" t="n">
-        <v>57644</v>
+        <v>79898</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5490,47 +5489,38 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>103021</v>
+        <v>6462</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>540316</v>
+        <v>540495</v>
       </c>
       <c r="R44" t="n">
-        <v>7200001</v>
+        <v>7199932</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5562,7 +5552,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>08:03</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5572,7 +5562,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>08:03</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5599,10 +5589,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123675725</v>
+        <v>123675762</v>
       </c>
       <c r="B45" t="n">
-        <v>78788</v>
+        <v>57507</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5615,34 +5605,39 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>540523</v>
+        <v>540423</v>
       </c>
       <c r="R45" t="n">
-        <v>7199906</v>
+        <v>7199851</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5674,7 +5669,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5684,7 +5679,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5711,10 +5706,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123675726</v>
+        <v>123675720</v>
       </c>
       <c r="B46" t="n">
-        <v>79898</v>
+        <v>57491</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5723,38 +5718,43 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>540524</v>
+        <v>540612</v>
       </c>
       <c r="R46" t="n">
-        <v>7199907</v>
+        <v>7199895</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5786,7 +5786,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5796,7 +5796,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5823,10 +5823,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123675774</v>
+        <v>123675778</v>
       </c>
       <c r="B47" t="n">
-        <v>78788</v>
+        <v>74879</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5839,21 +5839,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5863,10 +5863,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>540546</v>
+        <v>540666</v>
       </c>
       <c r="R47" t="n">
-        <v>7199996</v>
+        <v>7200065</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5898,7 +5898,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>07:56</t>
+          <t>07:38</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5908,7 +5908,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>07:56</t>
+          <t>07:38</t>
         </is>
       </c>
       <c r="AD47" t="b">

--- a/artfynd/A 9827-2025 artfynd.xlsx
+++ b/artfynd/A 9827-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123675779</v>
       </c>
       <c r="B2" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 9827-2025 artfynd.xlsx
+++ b/artfynd/A 9827-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123675779</v>
       </c>
       <c r="B2" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 9827-2025 artfynd.xlsx
+++ b/artfynd/A 9827-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123675779</v>
       </c>
       <c r="B2" t="n">
-        <v>57892</v>
+        <v>57897</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 9827-2025 artfynd.xlsx
+++ b/artfynd/A 9827-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY47"/>
+  <dimension ref="A1:AY53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,57 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123675779</v>
+        <v>123675763</v>
       </c>
       <c r="B2" t="n">
-        <v>57897</v>
+        <v>78350</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>(Kremp.) A.F.W.Schmidt</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>540603</v>
+        <v>540425</v>
       </c>
       <c r="R2" t="n">
-        <v>7199887</v>
+        <v>7199890</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>07:32</t>
+          <t>08:27</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>07:32</t>
+          <t>08:27</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,15 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123675763</v>
+        <v>123675738</v>
       </c>
       <c r="B3" t="n">
-        <v>77753</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>314</v>
+        <v>864</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -831,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>540425</v>
+        <v>540142</v>
       </c>
       <c r="R3" t="n">
-        <v>7199890</v>
+        <v>7199918</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -866,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>08:27</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -876,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>08:27</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,15 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123675738</v>
+        <v>123675746</v>
       </c>
       <c r="B4" t="n">
-        <v>78889</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -943,7 +924,7 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>540142</v>
+        <v>540241</v>
       </c>
       <c r="R4" t="n">
         <v>7199918</v>
@@ -978,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -988,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1015,55 +996,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123675727</v>
+        <v>123675764</v>
       </c>
       <c r="B5" t="n">
-        <v>56722</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>864</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>540500</v>
+        <v>540428</v>
       </c>
       <c r="R5" t="n">
-        <v>7199873</v>
+        <v>7199871</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1095,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>08:23</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1105,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>08:23</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1132,55 +1103,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123675718</v>
+        <v>123675748</v>
       </c>
       <c r="B6" t="n">
-        <v>56722</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>1312</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>540623</v>
+        <v>540241</v>
       </c>
       <c r="R6" t="n">
-        <v>7199942</v>
+        <v>7199916</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1212,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1222,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1249,37 +1210,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123675767</v>
+        <v>123675775</v>
       </c>
       <c r="B7" t="n">
-        <v>78896</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6450</v>
+        <v>1312</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1289,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>540427</v>
+        <v>540545</v>
       </c>
       <c r="R7" t="n">
-        <v>7199883</v>
+        <v>7199990</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1324,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>07:55</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1334,7 +1290,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>07:55</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1361,37 +1317,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123675722</v>
+        <v>123675741</v>
       </c>
       <c r="B8" t="n">
-        <v>79851</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>229497</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1401,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>540541</v>
+        <v>540183</v>
       </c>
       <c r="R8" t="n">
-        <v>7199839</v>
+        <v>7199904</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1436,7 +1387,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1446,7 +1397,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1473,37 +1424,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123675754</v>
+        <v>123675719</v>
       </c>
       <c r="B9" t="n">
-        <v>91030</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1513,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>540318</v>
+        <v>540622</v>
       </c>
       <c r="R9" t="n">
-        <v>7199932</v>
+        <v>7199937</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1548,7 +1494,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1558,7 +1504,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1585,59 +1531,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123675755</v>
+        <v>123675725</v>
       </c>
       <c r="B10" t="n">
-        <v>57666</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>540398</v>
+        <v>540523</v>
       </c>
       <c r="R10" t="n">
-        <v>7199894</v>
+        <v>7199906</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1669,7 +1601,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1679,7 +1611,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1706,19 +1638,14 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123675737</v>
+        <v>123675730</v>
       </c>
       <c r="B11" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1746,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>540120</v>
+        <v>540340</v>
       </c>
       <c r="R11" t="n">
-        <v>7199910</v>
+        <v>7200020</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1781,7 +1708,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1791,7 +1718,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1818,19 +1745,14 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123675736</v>
+        <v>123675732</v>
       </c>
       <c r="B12" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1858,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>540078</v>
+        <v>540171</v>
       </c>
       <c r="R12" t="n">
-        <v>7199948</v>
+        <v>7200163</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1893,7 +1815,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1903,7 +1825,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1930,55 +1852,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123675720</v>
+        <v>123675736</v>
       </c>
       <c r="B13" t="n">
-        <v>57513</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>540612</v>
+        <v>540078</v>
       </c>
       <c r="R13" t="n">
-        <v>7199895</v>
+        <v>7199948</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2010,7 +1922,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2020,7 +1932,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2047,19 +1959,14 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123675772</v>
+        <v>123675737</v>
       </c>
       <c r="B14" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -2087,10 +1994,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>540491</v>
+        <v>540120</v>
       </c>
       <c r="R14" t="n">
-        <v>7199896</v>
+        <v>7199910</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2122,7 +2029,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2132,7 +2039,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2159,55 +2066,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123675771</v>
+        <v>123675739</v>
       </c>
       <c r="B15" t="n">
-        <v>57513</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>540488</v>
+        <v>540140</v>
       </c>
       <c r="R15" t="n">
-        <v>7199896</v>
+        <v>7199918</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2239,7 +2136,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2249,7 +2146,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2276,37 +2173,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123675764</v>
+        <v>123675742</v>
       </c>
       <c r="B16" t="n">
-        <v>78889</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2316,10 +2208,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>540428</v>
+        <v>540183</v>
       </c>
       <c r="R16" t="n">
-        <v>7199871</v>
+        <v>7199904</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2351,7 +2243,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>08:23</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2361,7 +2253,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>08:23</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2388,37 +2280,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123675724</v>
+        <v>123675745</v>
       </c>
       <c r="B17" t="n">
-        <v>79927</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2428,10 +2315,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>540524</v>
+        <v>540181</v>
       </c>
       <c r="R17" t="n">
-        <v>7199906</v>
+        <v>7199901</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2463,7 +2350,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2473,7 +2360,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2500,59 +2387,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123675781</v>
+        <v>123675750</v>
       </c>
       <c r="B18" t="n">
-        <v>57883</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>540728</v>
+        <v>540220</v>
       </c>
       <c r="R18" t="n">
-        <v>7200067</v>
+        <v>7199934</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2584,7 +2457,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>07:29</t>
+          <t>08:57</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2594,7 +2467,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>07:29</t>
+          <t>08:57</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2621,37 +2494,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123675726</v>
+        <v>123675751</v>
       </c>
       <c r="B19" t="n">
-        <v>79920</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2661,10 +2529,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>540524</v>
+        <v>540269</v>
       </c>
       <c r="R19" t="n">
-        <v>7199907</v>
+        <v>7199949</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2696,7 +2564,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2706,7 +2574,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2733,19 +2601,14 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123675725</v>
+        <v>123675753</v>
       </c>
       <c r="B20" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -2773,10 +2636,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>540523</v>
+        <v>540320</v>
       </c>
       <c r="R20" t="n">
-        <v>7199906</v>
+        <v>7199929</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2808,7 +2671,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2818,7 +2681,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2845,19 +2708,14 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123675783</v>
+        <v>123675761</v>
       </c>
       <c r="B21" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -2885,10 +2743,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>540760</v>
+        <v>540369</v>
       </c>
       <c r="R21" t="n">
-        <v>7200064</v>
+        <v>7199910</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2920,7 +2778,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:37</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2930,7 +2788,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:37</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2957,19 +2815,14 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123675739</v>
+        <v>123675766</v>
       </c>
       <c r="B22" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -2997,10 +2850,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>540140</v>
+        <v>540428</v>
       </c>
       <c r="R22" t="n">
-        <v>7199918</v>
+        <v>7199871</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3032,7 +2885,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>08:23</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3042,7 +2895,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>08:23</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3069,19 +2922,14 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123675770</v>
+        <v>123675768</v>
       </c>
       <c r="B23" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -3109,10 +2957,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>540474</v>
+        <v>540469</v>
       </c>
       <c r="R23" t="n">
-        <v>7199895</v>
+        <v>7199898</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3144,7 +2992,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3154,7 +3002,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3181,55 +3029,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123675728</v>
+        <v>123675770</v>
       </c>
       <c r="B24" t="n">
-        <v>56722</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>540526</v>
+        <v>540474</v>
       </c>
       <c r="R24" t="n">
-        <v>7199833</v>
+        <v>7199895</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3261,7 +3099,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3271,7 +3109,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3298,59 +3136,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123675759</v>
+        <v>123675772</v>
       </c>
       <c r="B25" t="n">
-        <v>57883</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>540345</v>
+        <v>540491</v>
       </c>
       <c r="R25" t="n">
-        <v>7199934</v>
+        <v>7199896</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3382,7 +3206,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3392,7 +3216,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3419,19 +3243,14 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123675730</v>
+        <v>123675774</v>
       </c>
       <c r="B26" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -3459,10 +3278,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>540340</v>
+        <v>540546</v>
       </c>
       <c r="R26" t="n">
-        <v>7200020</v>
+        <v>7199996</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3494,7 +3313,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>07:56</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3504,7 +3323,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>07:56</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3531,37 +3350,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123675723</v>
+        <v>123675783</v>
       </c>
       <c r="B27" t="n">
-        <v>79920</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3571,10 +3385,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>540541</v>
+        <v>540760</v>
       </c>
       <c r="R27" t="n">
-        <v>7199839</v>
+        <v>7200064</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3606,7 +3420,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3616,7 +3430,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3643,15 +3457,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123675761</v>
+        <v>123675778</v>
       </c>
       <c r="B28" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3659,21 +3468,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3683,10 +3492,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>540369</v>
+        <v>540666</v>
       </c>
       <c r="R28" t="n">
-        <v>7199910</v>
+        <v>7200065</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3718,7 +3527,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>08:37</t>
+          <t>07:38</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3728,7 +3537,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>08:37</t>
+          <t>07:38</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3755,15 +3564,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123675766</v>
+        <v>123675767</v>
       </c>
       <c r="B29" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79413</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3771,21 +3575,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>6450</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3795,10 +3599,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>540428</v>
+        <v>540427</v>
       </c>
       <c r="R29" t="n">
-        <v>7199871</v>
+        <v>7199883</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3830,7 +3634,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>08:23</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3840,7 +3644,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>08:23</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3867,15 +3671,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123675780</v>
+        <v>123675723</v>
       </c>
       <c r="B30" t="n">
-        <v>58191</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3883,43 +3682,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>103044</v>
+        <v>6462</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>540723</v>
+        <v>540541</v>
       </c>
       <c r="R30" t="n">
-        <v>7200075</v>
+        <v>7199839</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3951,7 +3741,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>07:29</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3961,7 +3751,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>07:29</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3988,37 +3778,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123675751</v>
+        <v>123675726</v>
       </c>
       <c r="B31" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4028,10 +3813,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>540269</v>
+        <v>540524</v>
       </c>
       <c r="R31" t="n">
-        <v>7199949</v>
+        <v>7199907</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4063,7 +3848,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>08:54</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4073,7 +3858,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>08:54</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4100,55 +3885,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123675762</v>
+        <v>123675773</v>
       </c>
       <c r="B32" t="n">
-        <v>57529</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>6462</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>540423</v>
+        <v>540495</v>
       </c>
       <c r="R32" t="n">
-        <v>7199851</v>
+        <v>7199932</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4180,7 +3955,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>08:03</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4190,7 +3965,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>08:03</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4217,15 +3992,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123675773</v>
+        <v>123675724</v>
       </c>
       <c r="B33" t="n">
-        <v>79920</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4233,21 +4003,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6462</v>
+        <v>6464</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4257,10 +4027,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>540495</v>
+        <v>540524</v>
       </c>
       <c r="R33" t="n">
-        <v>7199932</v>
+        <v>7199906</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4292,7 +4062,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>08:03</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4302,7 +4072,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>08:03</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4329,37 +4099,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123675753</v>
+        <v>123675740</v>
       </c>
       <c r="B34" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4369,10 +4134,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>540320</v>
+        <v>540183</v>
       </c>
       <c r="R34" t="n">
-        <v>7199929</v>
+        <v>7199904</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4404,7 +4169,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4414,7 +4179,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4441,50 +4206,50 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123675778</v>
+        <v>123675743</v>
       </c>
       <c r="B35" t="n">
-        <v>74901</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6440</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>540666</v>
+        <v>540182</v>
       </c>
       <c r="R35" t="n">
-        <v>7200065</v>
+        <v>7199902</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4516,7 +4281,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>07:38</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4526,7 +4291,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>07:38</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4553,50 +4318,50 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123675774</v>
+        <v>123675749</v>
       </c>
       <c r="B36" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>540546</v>
+        <v>540220</v>
       </c>
       <c r="R36" t="n">
-        <v>7199996</v>
+        <v>7199936</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4628,7 +4393,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>07:56</t>
+          <t>08:57</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4638,7 +4403,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>07:56</t>
+          <t>08:57</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4665,47 +4430,38 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123675756</v>
+        <v>123675762</v>
       </c>
       <c r="B37" t="n">
-        <v>57666</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4714,10 +4470,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>540336</v>
+        <v>540423</v>
       </c>
       <c r="R37" t="n">
-        <v>7199942</v>
+        <v>7199851</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4749,7 +4505,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4759,7 +4515,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4786,15 +4542,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123675750</v>
+        <v>123675720</v>
       </c>
       <c r="B38" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4802,34 +4553,39 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>540220</v>
+        <v>540612</v>
       </c>
       <c r="R38" t="n">
-        <v>7199934</v>
+        <v>7199895</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4861,7 +4617,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>08:57</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4871,7 +4627,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>08:57</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4898,15 +4654,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123675749</v>
+        <v>123675735</v>
       </c>
       <c r="B39" t="n">
-        <v>57529</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4914,16 +4665,16 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -4934,7 +4685,7 @@
       <c r="I39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -4943,10 +4694,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>540220</v>
+        <v>540080</v>
       </c>
       <c r="R39" t="n">
-        <v>7199936</v>
+        <v>7199959</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4978,7 +4729,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>08:57</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4988,7 +4739,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>08:57</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5015,15 +4766,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123675775</v>
+        <v>123675752</v>
       </c>
       <c r="B40" t="n">
-        <v>82597</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5031,34 +4777,39 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>540545</v>
+        <v>540320</v>
       </c>
       <c r="R40" t="n">
-        <v>7199990</v>
+        <v>7199929</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -5090,7 +4841,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>07:55</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5100,7 +4851,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>07:55</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5127,15 +4878,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123675752</v>
+        <v>123675771</v>
       </c>
       <c r="B41" t="n">
-        <v>57513</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5172,10 +4918,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>540320</v>
+        <v>540488</v>
       </c>
       <c r="R41" t="n">
-        <v>7199929</v>
+        <v>7199896</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5207,7 +4953,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5217,7 +4963,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5244,15 +4990,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123675768</v>
+        <v>123675779</v>
       </c>
       <c r="B42" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5260,37 +5001,46 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>540469</v>
+        <v>540603</v>
       </c>
       <c r="R42" t="n">
-        <v>7199898</v>
+        <v>7199887</v>
       </c>
       <c r="S42" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5319,7 +5069,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>07:32</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5329,7 +5079,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>07:32</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5356,50 +5106,50 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123675719</v>
+        <v>123675718</v>
       </c>
       <c r="B43" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>540622</v>
+        <v>540623</v>
       </c>
       <c r="R43" t="n">
-        <v>7199937</v>
+        <v>7199942</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5468,47 +5218,38 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123675757</v>
+        <v>123675727</v>
       </c>
       <c r="B44" t="n">
-        <v>57666</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -5517,10 +5258,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>540316</v>
+        <v>540500</v>
       </c>
       <c r="R44" t="n">
-        <v>7200001</v>
+        <v>7199873</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5552,7 +5293,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5562,7 +5303,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5589,50 +5330,50 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123675732</v>
+        <v>123675728</v>
       </c>
       <c r="B45" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>540171</v>
+        <v>540526</v>
       </c>
       <c r="R45" t="n">
-        <v>7200163</v>
+        <v>7199833</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5664,7 +5405,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5674,7 +5415,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5701,32 +5442,27 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123675735</v>
+        <v>123675759</v>
       </c>
       <c r="B46" t="n">
-        <v>57513</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>103015</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -5734,10 +5470,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr"/>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -5746,10 +5486,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>540080</v>
+        <v>540345</v>
       </c>
       <c r="R46" t="n">
-        <v>7199959</v>
+        <v>7199934</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5781,7 +5521,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5791,7 +5531,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5818,15 +5558,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123675769</v>
+        <v>123675781</v>
       </c>
       <c r="B47" t="n">
-        <v>96979</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5834,34 +5569,43 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>221945</v>
+        <v>103015</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>540475</v>
+        <v>540728</v>
       </c>
       <c r="R47" t="n">
-        <v>7199900</v>
+        <v>7200067</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5893,7 +5637,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>07:29</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5903,7 +5647,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>07:29</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5927,6 +5671,684 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>123675755</v>
+      </c>
+      <c r="B48" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Gäddbäcksberget, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>540398</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7199894</v>
+      </c>
+      <c r="S48" t="n">
+        <v>25</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>08:49</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>08:49</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>123675756</v>
+      </c>
+      <c r="B49" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Gäddbäcksberget, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>540336</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7199942</v>
+      </c>
+      <c r="S49" t="n">
+        <v>25</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>08:49</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>08:49</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>123675757</v>
+      </c>
+      <c r="B50" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Gäddbäcksberget, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>540316</v>
+      </c>
+      <c r="R50" t="n">
+        <v>7200001</v>
+      </c>
+      <c r="S50" t="n">
+        <v>25</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>08:49</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>08:49</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>123675780</v>
+      </c>
+      <c r="B51" t="n">
+        <v>58636</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Gäddbäcksberget, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>540723</v>
+      </c>
+      <c r="R51" t="n">
+        <v>7200075</v>
+      </c>
+      <c r="S51" t="n">
+        <v>25</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>07:29</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>07:29</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>123675769</v>
+      </c>
+      <c r="B52" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Gäddbäcksberget, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>540475</v>
+      </c>
+      <c r="R52" t="n">
+        <v>7199900</v>
+      </c>
+      <c r="S52" t="n">
+        <v>25</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>123675722</v>
+      </c>
+      <c r="B53" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Gäddbäcksberget, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>540541</v>
+      </c>
+      <c r="R53" t="n">
+        <v>7199839</v>
+      </c>
+      <c r="S53" t="n">
+        <v>25</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>10:27</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>10:27</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
